--- a/output/yearly_surface_area_iteration_67_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_67_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497634701052</v>
+        <v>10.84497635505847</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907199346393</v>
+        <v>37.78907202150684</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.749695393146069</v>
+        <v>5.958226817073892</v>
       </c>
       <c r="C2" t="n">
-        <v>8.229991004701011</v>
+        <v>14.43463649554085</v>
       </c>
       <c r="D2" t="n">
-        <v>37.74230874206438</v>
+        <v>23.93697252494573</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.65182372235765</v>
+        <v>16.96460032938488</v>
       </c>
       <c r="C3" t="n">
-        <v>29.73713796163589</v>
+        <v>32.88854809226815</v>
       </c>
       <c r="D3" t="n">
-        <v>107.1773968726243</v>
+        <v>51.42394474844792</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.34371917414018</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="C4" t="n">
-        <v>76.64013453202725</v>
+        <v>86.90136153681492</v>
       </c>
       <c r="D4" t="n">
-        <v>119.101704488406</v>
+        <v>57.94274950464675</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.23402547317179</v>
+        <v>43.09872421643498</v>
       </c>
       <c r="C5" t="n">
-        <v>125.5655313731671</v>
+        <v>152.9072049364407</v>
       </c>
       <c r="D5" t="n">
-        <v>69.26230053461248</v>
+        <v>43.93320976504477</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.78121879733577</v>
+        <v>42.66675522656639</v>
       </c>
       <c r="C6" t="n">
-        <v>169.2582129506714</v>
+        <v>161.8116566139593</v>
       </c>
       <c r="D6" t="n">
-        <v>43.83405324691584</v>
+        <v>38.03781480104267</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.80545939030566</v>
+        <v>29.40432548989622</v>
       </c>
       <c r="C7" t="n">
-        <v>171.3355910928576</v>
+        <v>141.0329664535755</v>
       </c>
       <c r="D7" t="n">
-        <v>37.06981156465531</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.35315143608837</v>
+        <v>15.35453409442011</v>
       </c>
       <c r="C8" t="n">
-        <v>118.9141906768949</v>
+        <v>96.29963230956963</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>57.79843259212245</v>
+        <v>50.69843319500952</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
         <v>34.73423377625215</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.71549845441346</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.610864520522544</v>
+        <v>7.67371262906579</v>
       </c>
       <c r="C21" t="n">
-        <v>90.3790161812052</v>
+        <v>93.0437656274227</v>
       </c>
       <c r="D21" t="n">
-        <v>7.610864520522544</v>
+        <v>8.632926707699013</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.34954324044087</v>
+        <v>6.875179172840412</v>
       </c>
       <c r="C2" t="n">
-        <v>15.58524480491811</v>
+        <v>13.05528097107408</v>
       </c>
       <c r="D2" t="n">
-        <v>30.12591005251763</v>
+        <v>30.48032097375072</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.54244881655876</v>
+        <v>18.20160243673586</v>
       </c>
       <c r="C3" t="n">
-        <v>30.51271864799087</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D3" t="n">
-        <v>110.0980962927586</v>
+        <v>56.78428721363552</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.21234490822035</v>
+        <v>32.04719030972863</v>
       </c>
       <c r="C4" t="n">
-        <v>74.59809930719389</v>
+        <v>83.60857973677112</v>
       </c>
       <c r="D4" t="n">
-        <v>137.3141061498886</v>
+        <v>67.25953521794898</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.18555998276521</v>
+        <v>45.60218086226435</v>
       </c>
       <c r="C5" t="n">
-        <v>132.1677846842269</v>
+        <v>156.1224286678491</v>
       </c>
       <c r="D5" t="n">
-        <v>90.14898294246338</v>
+        <v>52.94074495150926</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.46928506929254</v>
+        <v>50.03280825153021</v>
       </c>
       <c r="C6" t="n">
-        <v>180.8909414982919</v>
+        <v>197.1123588155619</v>
       </c>
       <c r="D6" t="n">
-        <v>52.20639766873265</v>
+        <v>42.02272873258048</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.30935800449154</v>
+        <v>38.74663664350886</v>
       </c>
       <c r="C7" t="n">
-        <v>201.8777621719759</v>
+        <v>183.9716657942183</v>
       </c>
       <c r="D7" t="n">
-        <v>40.18391528252619</v>
+        <v>39.34550274309942</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.19593293468863</v>
+        <v>22.5311098124643</v>
       </c>
       <c r="C8" t="n">
-        <v>165.812278508765</v>
+        <v>136.5218357525615</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.31718662392973</v>
+        <v>10.98281156740907</v>
       </c>
       <c r="C9" t="n">
-        <v>94.51874197406589</v>
+        <v>81.20624310447914</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>47.26133448244146</v>
+        <v>45.12603322570465</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.58296251434014</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.770498335391403</v>
+        <v>7.846977797295708</v>
       </c>
       <c r="C21" t="n">
-        <v>98.10254148431648</v>
+        <v>101.0298391401822</v>
       </c>
       <c r="D21" t="n">
-        <v>8.74181062731533</v>
+        <v>9.808722246619634</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.535093556543517</v>
+        <v>8.399833357535709</v>
       </c>
       <c r="C2" t="n">
-        <v>10.83162242095506</v>
+        <v>14.15189315671777</v>
       </c>
       <c r="D2" t="n">
-        <v>33.71812490235671</v>
+        <v>34.72147105609695</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.57680998620739</v>
+        <v>19.82148614874311</v>
       </c>
       <c r="C3" t="n">
-        <v>42.83856107480958</v>
+        <v>47.1238898038469</v>
       </c>
       <c r="D3" t="n">
-        <v>107.7664454951724</v>
+        <v>64.62354263204629</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.55769911593697</v>
+        <v>32.25139383221197</v>
       </c>
       <c r="C4" t="n">
-        <v>74.18969226222723</v>
+        <v>93.9080949020244</v>
       </c>
       <c r="D4" t="n">
-        <v>151.8380816865159</v>
+        <v>76.78052445373456</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.92187076095032</v>
+        <v>46.16668579220627</v>
       </c>
       <c r="C5" t="n">
-        <v>133.7385810110218</v>
+        <v>153.2508166329271</v>
       </c>
       <c r="D5" t="n">
-        <v>110.7656847316464</v>
+        <v>61.08925089675779</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.38627848278806</v>
+        <v>54.46049039768332</v>
       </c>
       <c r="C6" t="n">
-        <v>190.752597187451</v>
+        <v>216.6746635703838</v>
       </c>
       <c r="D6" t="n">
-        <v>62.95358978712248</v>
+        <v>47.49695393146069</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.15450390912779</v>
+        <v>47.01098881785852</v>
       </c>
       <c r="C7" t="n">
-        <v>224.1555810767445</v>
+        <v>226.7307053049838</v>
       </c>
       <c r="D7" t="n">
-        <v>44.49575119957818</v>
+        <v>41.50142070162541</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.28906009787184</v>
+        <v>30.45872252425729</v>
       </c>
       <c r="C8" t="n">
-        <v>204.8662021837031</v>
+        <v>179.7481871705485</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.63668090063322</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.42187377538564</v>
+        <v>15.42031119060464</v>
       </c>
       <c r="C9" t="n">
-        <v>137.562488319063</v>
+        <v>116.7062400900438</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>70.60729488943061</v>
+        <v>65.90963212460962</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>40.33706792438868</v>
+        <v>40.51476425885736</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.914080696712187</v>
+        <v>8.002538864047999</v>
       </c>
       <c r="C21" t="n">
-        <v>104.8615692314365</v>
+        <v>108.034274664648</v>
       </c>
       <c r="D21" t="n">
-        <v>8.903340783801211</v>
+        <v>11.003490938066</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.253331965424683</v>
+        <v>7.673340056393069</v>
       </c>
       <c r="C2" t="n">
-        <v>7.798022014832415</v>
+        <v>9.96277570269663</v>
       </c>
       <c r="D2" t="n">
-        <v>28.21542902005333</v>
+        <v>28.39705234533899</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.69524160552276</v>
+        <v>22.72745935331366</v>
       </c>
       <c r="C3" t="n">
-        <v>58.33053984782424</v>
+        <v>67.63259934556277</v>
       </c>
       <c r="D3" t="n">
-        <v>115.7480543306989</v>
+        <v>68.00566347317655</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.98115117163684</v>
+        <v>22.18160762975243</v>
       </c>
       <c r="C4" t="n">
-        <v>104.5011526308475</v>
+        <v>126.0829124133051</v>
       </c>
       <c r="D4" t="n">
-        <v>138.0160557584251</v>
+        <v>72.0710807164626</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.19503330244241</v>
+        <v>30.67961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>113.9809084630547</v>
+        <v>129.4679784975481</v>
       </c>
       <c r="D5" t="n">
-        <v>66.31705742187205</v>
+        <v>44.79223900626073</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.01515248838698</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="C6" t="n">
-        <v>147.6430737462694</v>
+        <v>149.3336432929823</v>
       </c>
       <c r="D6" t="n">
-        <v>29.3032054763588</v>
+        <v>27.33087433852696</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.74450891718435</v>
+        <v>20.18178755620168</v>
       </c>
       <c r="C7" t="n">
-        <v>144.0272969515283</v>
+        <v>126.360747013607</v>
       </c>
       <c r="D7" t="n">
-        <v>26.94897448157494</v>
+        <v>27.12863431145211</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.01382658331747</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>101.3899941560893</v>
+        <v>85.95201150680825</v>
       </c>
       <c r="D8" t="n">
-        <v>26.11939767148639</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>53.91562042182632</v>
+        <v>50.25468323268996</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.665445017030089</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>25.41057582902019</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>23.21538796232432</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>25.81898287398687</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.47216389248049</v>
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
-        <v>8.425358797846126</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>71.28470080536088</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>6.052474596681584</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.400774047510951</v>
+        <v>4.540583132141498</v>
       </c>
       <c r="C2" t="n">
-        <v>5.003968048545993</v>
+        <v>4.979424355939822</v>
       </c>
       <c r="D2" t="n">
-        <v>19.36202822315559</v>
+        <v>21.10266690278519</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.93929587325272</v>
+        <v>24.94130042639022</v>
       </c>
       <c r="C3" t="n">
-        <v>45.7690779719863</v>
+        <v>54.33482669153972</v>
       </c>
       <c r="D3" t="n">
-        <v>113.6176618124834</v>
+        <v>73.66543898815942</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.14554500660256</v>
+        <v>30.97512181669111</v>
       </c>
       <c r="C4" t="n">
-        <v>126.7082857009103</v>
+        <v>150.7532504733232</v>
       </c>
       <c r="D4" t="n">
-        <v>157.0325087896858</v>
+        <v>86.33980184998573</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.5820628820939</v>
+        <v>33.64940256305943</v>
       </c>
       <c r="C5" t="n">
-        <v>149.6428938198201</v>
+        <v>177.450897542611</v>
       </c>
       <c r="D5" t="n">
-        <v>88.50455553784997</v>
+        <v>55.07604620824608</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.24157635516951</v>
+        <v>34.13340418125311</v>
       </c>
       <c r="C6" t="n">
-        <v>167.3663851245878</v>
+        <v>177.5903057166141</v>
       </c>
       <c r="D6" t="n">
-        <v>36.66925850132262</v>
+        <v>31.75855648468008</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.24734366820796</v>
+        <v>18.68462230722529</v>
       </c>
       <c r="C7" t="n">
-        <v>173.0124161717111</v>
+        <v>161.8136201093678</v>
       </c>
       <c r="D7" t="n">
-        <v>29.46421209985527</v>
+        <v>29.2845522699781</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>131.2645767963198</v>
+        <v>111.7376149588507</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.215624642035802</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>54.47030787472577</v>
+        <v>54.24843289356598</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95624762613216</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.850594422505238</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>24.71549845441346</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>61.98656829843935</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>4.814490741626358</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.82292556033708</v>
+        <v>3.881830422591888</v>
       </c>
       <c r="C2" t="n">
-        <v>12.15403657857551</v>
+        <v>6.836891012374788</v>
       </c>
       <c r="D2" t="n">
-        <v>15.14738532882404</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.9730351480956</v>
+        <v>20.19455027635689</v>
       </c>
       <c r="C3" t="n">
-        <v>32.89345683078938</v>
+        <v>36.56028450615122</v>
       </c>
       <c r="D3" t="n">
-        <v>104.0112605264283</v>
+        <v>73.7488875430204</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.22136056400782</v>
+        <v>38.7220929509027</v>
       </c>
       <c r="C4" t="n">
-        <v>120.5821800264102</v>
+        <v>143.1466692608189</v>
       </c>
       <c r="D4" t="n">
-        <v>173.50918051006</v>
+        <v>99.03870840441823</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.17173339944774</v>
+        <v>39.29445186247859</v>
       </c>
       <c r="C5" t="n">
-        <v>187.1456561220483</v>
+        <v>224.5011562686394</v>
       </c>
       <c r="D5" t="n">
-        <v>116.5334524940964</v>
+        <v>70.44039777970866</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.11831811279092</v>
+        <v>39.08435785376978</v>
       </c>
       <c r="C6" t="n">
-        <v>198.0381469006666</v>
+        <v>226.6570742271654</v>
       </c>
       <c r="D6" t="n">
-        <v>50.75733805726436</v>
+        <v>39.7686360036298</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.03260296288517</v>
+        <v>27.12863431145211</v>
       </c>
       <c r="C7" t="n">
-        <v>205.1715257197239</v>
+        <v>205.4709587695192</v>
       </c>
       <c r="D7" t="n">
-        <v>32.33876937788993</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>12.76762889372977</v>
       </c>
       <c r="C8" t="n">
-        <v>173.3226484462531</v>
+        <v>156.2156946997524</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>96.07186684218435</v>
+        <v>87.97343002985241</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>44.98367980858886</v>
+        <v>45.55309347705201</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>23.21538796232432</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.46605242207675</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>6.42062998577414</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31.89600116327462</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>3.009056713516474</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.336559536107409</v>
+        <v>2.359139733305085</v>
       </c>
       <c r="C2" t="n">
-        <v>6.043638867343365</v>
+        <v>3.365431130158066</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6814150222053</v>
+        <v>13.75330358879357</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.22338081267854</v>
+        <v>19.50241814486289</v>
       </c>
       <c r="C3" t="n">
-        <v>40.57563261652067</v>
+        <v>34.52806675836032</v>
       </c>
       <c r="D3" t="n">
-        <v>99.13197443632168</v>
+        <v>74.49501579824798</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.16954891986099</v>
+        <v>42.05316291141212</v>
       </c>
       <c r="C4" t="n">
-        <v>119.5483996938383</v>
+        <v>140.5047861886908</v>
       </c>
       <c r="D4" t="n">
-        <v>185.1615440117654</v>
+        <v>108.5979858006694</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.5216364927871</v>
+        <v>41.08614142272902</v>
       </c>
       <c r="C5" t="n">
-        <v>226.7837196810133</v>
+        <v>270.0787934382976</v>
       </c>
       <c r="D5" t="n">
-        <v>119.6750451476862</v>
+        <v>72.77204857729483</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.94723197034471</v>
+        <v>32.00006641992479</v>
       </c>
       <c r="C6" t="n">
-        <v>231.1250080291927</v>
+        <v>262.3200413316351</v>
       </c>
       <c r="D6" t="n">
-        <v>49.30827844579606</v>
+        <v>39.44662275663685</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>8.444012004226815</v>
       </c>
       <c r="C7" t="n">
-        <v>216.4302083920263</v>
+        <v>208.8844955371853</v>
       </c>
       <c r="D7" t="n">
-        <v>32.33876937788993</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.75518496874405</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>118.3300507928681</v>
+        <v>109.2341583130213</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
-        <v>30.7296848906294</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>22.776546738526</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>18.48041878474196</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>22.38973814305275</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.10280577150543</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.18348900970292</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>5.194427103169874</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27.28767743954009</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>2.140209995258047</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.974695543867836</v>
+        <v>2.595740930028567</v>
       </c>
       <c r="C2" t="n">
-        <v>10.93372418219673</v>
+        <v>5.846307578789756</v>
       </c>
       <c r="D2" t="n">
-        <v>14.70854410502571</v>
+        <v>15.24850534236146</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.39456476611598</v>
+        <v>14.14698441819654</v>
       </c>
       <c r="C3" t="n">
-        <v>32.39276550162351</v>
+        <v>24.02827506144068</v>
       </c>
       <c r="D3" t="n">
-        <v>87.72406611297374</v>
+        <v>68.87451019143498</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.57871672835365</v>
+        <v>39.6282460819225</v>
       </c>
       <c r="C4" t="n">
-        <v>111.9928693619549</v>
+        <v>116.038651651156</v>
       </c>
       <c r="D4" t="n">
-        <v>189.973089510279</v>
+        <v>118.361466719404</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.11759840699392</v>
+        <v>49.99550183876883</v>
       </c>
       <c r="C5" t="n">
-        <v>223.3476027161494</v>
+        <v>264.5073752166969</v>
       </c>
       <c r="D5" t="n">
-        <v>147.8021168743573</v>
+        <v>90.83620633543615</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.80259626265094</v>
+        <v>40.8151790563569</v>
       </c>
       <c r="C6" t="n">
-        <v>289.0471408320502</v>
+        <v>337.9529027191051</v>
       </c>
       <c r="D6" t="n">
-        <v>66.97875537453442</v>
+        <v>48.90576188705487</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.63040519931347</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="C7" t="n">
-        <v>264.638929409066</v>
+        <v>278.3529630896896</v>
       </c>
       <c r="D7" t="n">
-        <v>37.12969817461437</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>181.58405537749</v>
+        <v>173.6564426656971</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>32.71183350550372</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>71.44374393344886</v>
+        <v>69.22499412185107</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>21.50125647070939</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.30897278939726</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.46681318560274</v>
@@ -3159,7 +3159,7 @@
         <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>3.777765165941727</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.96055016538088</v>
+        <v>1.777945092390974</v>
       </c>
       <c r="C2" t="n">
-        <v>6.135923151542564</v>
+        <v>4.963716392671873</v>
       </c>
       <c r="D2" t="n">
-        <v>12.06175229437631</v>
+        <v>12.13341987678633</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.51590057081509</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C3" t="n">
-        <v>36.89898746411637</v>
+        <v>23.89083038284613</v>
       </c>
       <c r="D3" t="n">
-        <v>82.34408869370122</v>
+        <v>66.06180301876786</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.57947749187965</v>
+        <v>35.77390459504952</v>
       </c>
       <c r="C4" t="n">
-        <v>102.4846428463245</v>
+        <v>95.79697748499525</v>
       </c>
       <c r="D4" t="n">
-        <v>190.4070219955561</v>
+        <v>123.4665547814874</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.79286090106649</v>
+        <v>54.09429850399926</v>
       </c>
       <c r="C5" t="n">
-        <v>224.6729621168826</v>
+        <v>255.2544031041707</v>
       </c>
       <c r="D5" t="n">
-        <v>165.5962940138308</v>
+        <v>104.2616061910113</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.87430490278997</v>
+        <v>47.0944373727195</v>
       </c>
       <c r="C6" t="n">
-        <v>322.2145052723245</v>
+        <v>379.0900950224549</v>
       </c>
       <c r="D6" t="n">
-        <v>81.59010645683969</v>
+        <v>56.95609306187872</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.77392029058275</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="C7" t="n">
-        <v>314.1052692352457</v>
+        <v>345.725399293627</v>
       </c>
       <c r="D7" t="n">
-        <v>41.14210104187108</v>
+        <v>38.50709020367265</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>225.5614437892259</v>
+        <v>219.7200449489574</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.442187377538564</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>74.88280614142545</v>
+        <v>73.32968127330699</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>24.20008090968388</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>20.96816746730337</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>19.09302935219197</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.06233313145306</v>
+      </c>
+      <c r="D14" t="n">
         <v>10.75504610002381</v>
-      </c>
-      <c r="D14" t="n">
-        <v>10.44775906859456</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.820561154301086</v>
+        <v>2.595740930028567</v>
       </c>
       <c r="C2" t="n">
-        <v>17.23458094805276</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="D2" t="n">
-        <v>10.60974743979528</v>
+        <v>16.03390350575891</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.238245896962486</v>
+        <v>9.321694451823465</v>
       </c>
       <c r="C3" t="n">
-        <v>31.31284302695202</v>
+        <v>21.8684301120977</v>
       </c>
       <c r="D3" t="n">
-        <v>74.73554398578844</v>
+        <v>61.33468782281948</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.64855968407542</v>
+        <v>29.86476516318797</v>
       </c>
       <c r="C4" t="n">
-        <v>96.84352053772237</v>
+        <v>80.54552689952106</v>
       </c>
       <c r="D4" t="n">
-        <v>187.7906643637384</v>
+        <v>126.197776894702</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.46750150033328</v>
+        <v>53.6525120370882</v>
       </c>
       <c r="C5" t="n">
-        <v>209.6522222419064</v>
+        <v>220.8932334555324</v>
       </c>
       <c r="D5" t="n">
-        <v>185.5748597952534</v>
+        <v>117.7115497391926</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.07935130425731</v>
+        <v>55.94980166502573</v>
       </c>
       <c r="C6" t="n">
-        <v>336.1013265488956</v>
+        <v>394.1844659752496</v>
       </c>
       <c r="D6" t="n">
-        <v>102.4404641996334</v>
+        <v>68.79007988886977</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.97271635292611</v>
+        <v>27.66761380108361</v>
       </c>
       <c r="C7" t="n">
-        <v>373.6924461445059</v>
+        <v>420.4040019125691</v>
       </c>
       <c r="D7" t="n">
-        <v>49.34656660626167</v>
+        <v>43.5375654402333</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.759332943739289</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>291.9864934585651</v>
+        <v>304.33687957799</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>141.6671754705189</v>
+        <v>140.4468630741401</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>47.97310156802039</v>
+        <v>49.11192890494669</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05518316008284</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>19.30999559483051</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>10.44775906859456</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>25.21226279276234</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>2.479894700927443</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.776022654711485</v>
+        <v>5.86005204664921</v>
       </c>
       <c r="C2" t="n">
-        <v>16.55422978900972</v>
+        <v>11.55517047898496</v>
       </c>
       <c r="D2" t="n">
-        <v>6.981207924899069</v>
+        <v>4.080143458849744</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.081305133003238</v>
+        <v>1.918335014098267</v>
       </c>
       <c r="C2" t="n">
-        <v>10.34074856883165</v>
+        <v>2.91480893390878</v>
       </c>
       <c r="D2" t="n">
-        <v>7.977681844709581</v>
+        <v>11.92921635430299</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.35038611942488</v>
+        <v>12.68418033886879</v>
       </c>
       <c r="C3" t="n">
-        <v>46.25995182410971</v>
+        <v>25.0247489812512</v>
       </c>
       <c r="D3" t="n">
-        <v>79.83572330935061</v>
+        <v>67.09754684674826</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.1950743601714</v>
+        <v>41.04490801915065</v>
       </c>
       <c r="C4" t="n">
-        <v>133.3193747413084</v>
+        <v>118.731585603905</v>
       </c>
       <c r="D4" t="n">
-        <v>189.9348013498134</v>
+        <v>126.7338111412208</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.76520773443155</v>
+        <v>31.51410130632262</v>
       </c>
       <c r="C5" t="n">
-        <v>297.4940980793897</v>
+        <v>333.3278892843983</v>
       </c>
       <c r="D5" t="n">
-        <v>163.0437499827891</v>
+        <v>104.5806741948915</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.49688751153591</v>
+        <v>17.14720540237479</v>
       </c>
       <c r="C6" t="n">
-        <v>298.8282932094612</v>
+        <v>342.5818431446288</v>
       </c>
       <c r="D6" t="n">
-        <v>77.76619914879835</v>
+        <v>58.24414604985053</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.431609136970102</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>205.3511855496011</v>
+        <v>214.0347439936641</v>
       </c>
       <c r="D7" t="n">
-        <v>29.76364514965055</v>
+        <v>29.88341836956866</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.335176877775662</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>104.3941421310846</v>
+        <v>103.4762080276138</v>
       </c>
       <c r="D8" t="n">
-        <v>23.36559536107409</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2218749811597791</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>36.60937189136354</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="D9" t="n">
-        <v>19.081248379741</v>
+        <v>19.85781081380023</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>19.64477156197868</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>18.64829764216817</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.21570675749381</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>15.45958109877452</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>12.80100831567416</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>8.585383673638358</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>1.791689560250429</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.506042036043612</v>
+        <v>6.723990026386404</v>
       </c>
       <c r="C2" t="n">
-        <v>10.7884255219682</v>
+        <v>6.468735623282234</v>
       </c>
       <c r="D2" t="n">
-        <v>9.871473166201678</v>
+        <v>5.950372835439918</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.39242134425824</v>
+        <v>12.44856088984956</v>
       </c>
       <c r="C3" t="n">
-        <v>41.71445995344698</v>
+        <v>29.11863690796039</v>
       </c>
       <c r="D3" t="n">
-        <v>8.997717709422018</v>
+        <v>6.562983402889927</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39680015321422</v>
+        <v>13.39831182476694</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13618903741563</v>
+        <v>70.14410308260341</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576094135672261</v>
+        <v>1.576271979384346</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.235079669671493</v>
+        <v>5.391758391723482</v>
       </c>
       <c r="C2" t="n">
-        <v>5.020657759518188</v>
+        <v>6.66999390265283</v>
       </c>
       <c r="D2" t="n">
-        <v>24.82741769269759</v>
+        <v>13.37042198413731</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.27661617288612</v>
+        <v>18.9133695223148</v>
       </c>
       <c r="C3" t="n">
-        <v>41.94026192542374</v>
+        <v>26.6839026014283</v>
       </c>
       <c r="D3" t="n">
-        <v>15.11400590687965</v>
+        <v>9.974556675147594</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.69363796301277</v>
+        <v>14.48568737616169</v>
       </c>
       <c r="C4" t="n">
-        <v>64.09438061945727</v>
+        <v>44.88648678586841</v>
       </c>
       <c r="D4" t="n">
-        <v>19.78221624057323</v>
+        <v>18.50594422505237</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>39.82655911818034</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43542446084463</v>
+        <v>15.44175864368577</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11342067629111</v>
+        <v>86.14875874898378</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249563044388343</v>
+        <v>3.250896556565426</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.129631754689584</v>
+        <v>5.05698242457532</v>
       </c>
       <c r="C2" t="n">
-        <v>9.228428419920018</v>
+        <v>8.994772466309277</v>
       </c>
       <c r="D2" t="n">
-        <v>36.37473419004857</v>
+        <v>15.15229406734527</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.50870954171587</v>
+        <v>18.78574232076272</v>
       </c>
       <c r="C3" t="n">
-        <v>28.55413197801848</v>
+        <v>26.24211613451724</v>
       </c>
       <c r="D3" t="n">
-        <v>31.46501392111027</v>
+        <v>18.35377333089412</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.02693346083794</v>
+        <v>27.0697294491973</v>
       </c>
       <c r="C4" t="n">
-        <v>87.78198922752429</v>
+        <v>57.81512230309466</v>
       </c>
       <c r="D4" t="n">
-        <v>22.92184539875453</v>
+        <v>19.36104647545135</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.40714755982195</v>
+        <v>12.66454538478386</v>
       </c>
       <c r="C5" t="n">
-        <v>68.69779560467057</v>
+        <v>49.55371537185777</v>
       </c>
       <c r="D5" t="n">
-        <v>30.06602344255857</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.43776166510284</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.01453059358123</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.78845088416398</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>40.93593402397924</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.71758237398082</v>
+        <v>16.73455514787586</v>
       </c>
       <c r="C21" t="n">
-        <v>101.141373362584</v>
+        <v>102.0807864020427</v>
       </c>
       <c r="D21" t="n">
-        <v>4.179395593495205</v>
+        <v>5.020366544362757</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.882632243846888</v>
+        <v>5.432991795301848</v>
       </c>
       <c r="C2" t="n">
-        <v>6.977280934082081</v>
+        <v>11.51884581392783</v>
       </c>
       <c r="D2" t="n">
-        <v>40.46174988282804</v>
+        <v>17.35533591567511</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.83973844449629</v>
+        <v>18.14760631300229</v>
       </c>
       <c r="C3" t="n">
-        <v>32.54002765726053</v>
+        <v>31.22939447209104</v>
       </c>
       <c r="D3" t="n">
-        <v>50.9576145889307</v>
+        <v>25.78560345204247</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.80844569114741</v>
+        <v>31.81746134693488</v>
       </c>
       <c r="C4" t="n">
-        <v>78.92466143980957</v>
+        <v>62.2054980364864</v>
       </c>
       <c r="D4" t="n">
-        <v>32.17481751128071</v>
+        <v>23.94286301117121</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.90617849321559</v>
+        <v>26.50718801466389</v>
       </c>
       <c r="C5" t="n">
-        <v>116.5825398793088</v>
+        <v>80.45422436302613</v>
       </c>
       <c r="D5" t="n">
-        <v>31.56318869153496</v>
+        <v>29.32971266437347</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.3572583533546</v>
+        <v>11.63272854762046</v>
       </c>
       <c r="C6" t="n">
-        <v>61.34352355215771</v>
+        <v>46.36990756698535</v>
       </c>
       <c r="D6" t="n">
-        <v>37.39378830705677</v>
+        <v>38.03781480104267</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
         <v>39.76470901281281</v>
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>49.53898915629405</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5591,7 +5591,7 @@
         <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.02193293689738</v>
+        <v>18.05805012735702</v>
       </c>
       <c r="C21" t="n">
-        <v>115.8552831657688</v>
+        <v>117.8072794022815</v>
       </c>
       <c r="D21" t="n">
-        <v>6.007310978965791</v>
+        <v>6.879257191374101</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.896777622333842</v>
+        <v>5.373105185342792</v>
       </c>
       <c r="C2" t="n">
-        <v>8.652142517527139</v>
+        <v>12.26399232145116</v>
       </c>
       <c r="D2" t="n">
-        <v>48.28333384256238</v>
+        <v>18.42151392248715</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.22476347101029</v>
+        <v>16.38046044535803</v>
       </c>
       <c r="C3" t="n">
-        <v>27.64110661306895</v>
+        <v>36.61918936840603</v>
       </c>
       <c r="D3" t="n">
-        <v>65.05060288339365</v>
+        <v>31.26866438026091</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.41057582902019</v>
+        <v>24.5299481383108</v>
       </c>
       <c r="C4" t="n">
-        <v>66.22575488537709</v>
+        <v>59.52532680389261</v>
       </c>
       <c r="D4" t="n">
-        <v>42.05316291141212</v>
+        <v>27.10801760966293</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.51285751671111</v>
+        <v>22.60474089028281</v>
       </c>
       <c r="C5" t="n">
-        <v>97.58572180213298</v>
+        <v>73.50835935547994</v>
       </c>
       <c r="D5" t="n">
-        <v>29.01064466049325</v>
+        <v>25.13274122871835</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.24279478258523</v>
+        <v>12.92078153559227</v>
       </c>
       <c r="C6" t="n">
-        <v>82.31463626257383</v>
+        <v>59.37119241432587</v>
       </c>
       <c r="D6" t="n">
-        <v>30.18874190558942</v>
+        <v>30.22899356146354</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.749114556069321</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>34.37491411649782</v>
+        <v>28.44613973055133</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35868206941536</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>33.7623035490478</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5986,7 +5986,7 @@
         <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>19.79694245613693</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.033062648401315</v>
+        <v>7.055996145122117</v>
       </c>
       <c r="C21" t="n">
-        <v>65.05582949771217</v>
+        <v>66.14996386051985</v>
       </c>
       <c r="D21" t="n">
-        <v>4.395664155250822</v>
+        <v>5.291997108841588</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.786420968830701</v>
+        <v>4.944081438586937</v>
       </c>
       <c r="C2" t="n">
-        <v>8.339946747576654</v>
+        <v>6.080945280104743</v>
       </c>
       <c r="D2" t="n">
-        <v>46.23638987920778</v>
+        <v>16.58171872472863</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.12721059539136</v>
+        <v>17.87271695581319</v>
       </c>
       <c r="C3" t="n">
-        <v>31.37665662772806</v>
+        <v>43.90866607243859</v>
       </c>
       <c r="D3" t="n">
-        <v>88.58309535418971</v>
+        <v>39.18645961501144</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.32422308877548</v>
+        <v>29.09900195387546</v>
       </c>
       <c r="C4" t="n">
-        <v>68.08911202803753</v>
+        <v>79.86910273129502</v>
       </c>
       <c r="D4" t="n">
-        <v>64.75804206752811</v>
+        <v>36.94807484932871</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.48955761371645</v>
+        <v>31.14594591723007</v>
       </c>
       <c r="C5" t="n">
-        <v>112.1155878249858</v>
+        <v>95.96583809012573</v>
       </c>
       <c r="D5" t="n">
-        <v>38.06726723217008</v>
+        <v>29.7960428238907</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.46671537461151</v>
+        <v>22.98369550412208</v>
       </c>
       <c r="C6" t="n">
-        <v>122.3247822014483</v>
+        <v>93.26308666033425</v>
       </c>
       <c r="D6" t="n">
-        <v>32.92585450502953</v>
+        <v>31.87931145230244</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.13890945238431</v>
+        <v>11.31856928226148</v>
       </c>
       <c r="C7" t="n">
-        <v>81.80510920406972</v>
+        <v>61.86286808770426</v>
       </c>
       <c r="D7" t="n">
-        <v>32.45854259780804</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>33.62976760897448</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>22.96406055003713</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.05772749256809</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6266,10 +6266,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.241862628049939</v>
+        <v>7.276669185086543</v>
       </c>
       <c r="C21" t="n">
-        <v>74.22909193751188</v>
+        <v>75.49544279527288</v>
       </c>
       <c r="D21" t="n">
-        <v>5.431396971037454</v>
+        <v>6.367085536950724</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.517021187239575</v>
+        <v>4.868486865359933</v>
       </c>
       <c r="C2" t="n">
-        <v>7.212900383101315</v>
+        <v>8.744426801726341</v>
       </c>
       <c r="D2" t="n">
-        <v>35.73168944376691</v>
+        <v>24.01649408898972</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.36635612460008</v>
+        <v>17.60764507566654</v>
       </c>
       <c r="C3" t="n">
-        <v>31.9018916495001</v>
+        <v>31.80862561759665</v>
       </c>
       <c r="D3" t="n">
-        <v>104.0210780034708</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.99087083768807</v>
+        <v>32.13652935081509</v>
       </c>
       <c r="C4" t="n">
-        <v>73.79404793741575</v>
+        <v>97.29021574315466</v>
       </c>
       <c r="D4" t="n">
-        <v>92.97641633069418</v>
+        <v>48.28137034715389</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.43542262126263</v>
+        <v>38.2145293878071</v>
       </c>
       <c r="C5" t="n">
-        <v>118.2760546691345</v>
+        <v>124.0192787389783</v>
       </c>
       <c r="D5" t="n">
-        <v>51.8362787842316</v>
+        <v>36.12831551628263</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.2881194078966</v>
+        <v>33.12711278440013</v>
       </c>
       <c r="C6" t="n">
-        <v>151.7084909895554</v>
+        <v>126.0279345418673</v>
       </c>
       <c r="D6" t="n">
-        <v>36.95102009244145</v>
+        <v>34.49566908412018</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.3433750167749</v>
+        <v>19.94224111636546</v>
       </c>
       <c r="C7" t="n">
-        <v>130.8522427605361</v>
+        <v>101.7473503204352</v>
       </c>
       <c r="D7" t="n">
-        <v>34.85400699617026</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>71.01472018669303</v>
+        <v>57.57950285407543</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>32.9484347022272</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>25.58827216348886</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6636,7 +6636,7 @@
         <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.434515695355164</v>
+        <v>7.483323584886019</v>
       </c>
       <c r="C21" t="n">
-        <v>82.7089871108262</v>
+        <v>84.18739032996771</v>
       </c>
       <c r="D21" t="n">
-        <v>6.505201233435768</v>
+        <v>7.483323584886019</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_67_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_67_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497635505847</v>
+        <v>10.84497645002496</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907202150684</v>
+        <v>37.78907235241539</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.958226817073892</v>
+        <v>4.654465865834128</v>
       </c>
       <c r="C2" t="n">
-        <v>14.43463649554085</v>
+        <v>9.81256830394687</v>
       </c>
       <c r="D2" t="n">
-        <v>23.93697252494573</v>
+        <v>24.86766934857171</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.96460032938488</v>
+        <v>15.33489914033518</v>
       </c>
       <c r="C3" t="n">
-        <v>32.88854809226815</v>
+        <v>35.74052517310513</v>
       </c>
       <c r="D3" t="n">
-        <v>51.42394474844792</v>
+        <v>83.10985190301373</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.76190263842031</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="C4" t="n">
-        <v>86.90136153681492</v>
+        <v>81.24747650805753</v>
       </c>
       <c r="D4" t="n">
-        <v>57.94274950464675</v>
+        <v>95.63106212297755</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.09872421643498</v>
+        <v>38.23907308041327</v>
       </c>
       <c r="C5" t="n">
-        <v>152.9072049364407</v>
+        <v>133.9594742444773</v>
       </c>
       <c r="D5" t="n">
-        <v>43.93320976504477</v>
+        <v>66.58703804053992</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.66675522656639</v>
+        <v>33.85164259013428</v>
       </c>
       <c r="C6" t="n">
-        <v>161.8116566139593</v>
+        <v>165.3538023308818</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>45.24286120251001</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.40432548989622</v>
+        <v>23.1162314441954</v>
       </c>
       <c r="C7" t="n">
-        <v>141.0329664535755</v>
+        <v>163.6102184081394</v>
       </c>
       <c r="D7" t="n">
-        <v>36.83026512481909</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.35453409442011</v>
+        <v>12.2669375645639</v>
       </c>
       <c r="C8" t="n">
-        <v>96.29963230956963</v>
+        <v>110.2355409713531</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>35.04839304161113</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>50.69843319500952</v>
+        <v>56.68905768632355</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.67371262906579</v>
+        <v>7.637722181383358</v>
       </c>
       <c r="C21" t="n">
-        <v>93.0437656274227</v>
+        <v>91.65266617660029</v>
       </c>
       <c r="D21" t="n">
-        <v>8.632926707699013</v>
+        <v>7.637722181383358</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.875179172840412</v>
+        <v>6.14377713317654</v>
       </c>
       <c r="C2" t="n">
-        <v>13.05528097107408</v>
+        <v>14.44543572028757</v>
       </c>
       <c r="D2" t="n">
-        <v>30.48032097375072</v>
+        <v>22.32494279457247</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.20160243673586</v>
+        <v>15.22690689286803</v>
       </c>
       <c r="C3" t="n">
-        <v>44.12955930589413</v>
+        <v>36.62900684544849</v>
       </c>
       <c r="D3" t="n">
-        <v>56.78428721363552</v>
+        <v>82.93313731624932</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.04719030972863</v>
+        <v>29.52017171899734</v>
       </c>
       <c r="C4" t="n">
-        <v>83.60857973677112</v>
+        <v>84.82103815151592</v>
       </c>
       <c r="D4" t="n">
-        <v>67.25953521794898</v>
+        <v>111.2143434324872</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.60218086226435</v>
+        <v>41.77336481570179</v>
       </c>
       <c r="C5" t="n">
-        <v>156.1224286678491</v>
+        <v>139.5063487734718</v>
       </c>
       <c r="D5" t="n">
-        <v>52.94074495150926</v>
+        <v>80.79783605951251</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.03280825153021</v>
+        <v>41.17744395922398</v>
       </c>
       <c r="C6" t="n">
-        <v>197.1123588155619</v>
+        <v>185.1576170209485</v>
       </c>
       <c r="D6" t="n">
-        <v>42.02272873258048</v>
+        <v>53.81646390369741</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.74663664350886</v>
+        <v>30.3625112492411</v>
       </c>
       <c r="C7" t="n">
-        <v>183.9716657942183</v>
+        <v>198.2246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>39.34550274309942</v>
+        <v>41.74096714146164</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.5311098124643</v>
+        <v>17.69109363052752</v>
       </c>
       <c r="C8" t="n">
-        <v>136.5218357525615</v>
+        <v>156.3825918094744</v>
       </c>
       <c r="D8" t="n">
-        <v>37.1346069131356</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.98281156740907</v>
+        <v>9.207811718130833</v>
       </c>
       <c r="C9" t="n">
-        <v>81.20624310447914</v>
+        <v>91.85624220014853</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="C10" t="n">
-        <v>45.12603322570465</v>
+        <v>46.97662764820988</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.846977797295708</v>
+        <v>7.804251819638826</v>
       </c>
       <c r="C21" t="n">
-        <v>101.0298391401822</v>
+        <v>99.50421070039503</v>
       </c>
       <c r="D21" t="n">
-        <v>9.808722246619634</v>
+        <v>8.77978329709368</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.399833357535709</v>
+        <v>5.925829142833748</v>
       </c>
       <c r="C2" t="n">
-        <v>14.15189315671777</v>
+        <v>13.47841423160446</v>
       </c>
       <c r="D2" t="n">
-        <v>34.72147105609695</v>
+        <v>24.31789063419349</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.82148614874311</v>
+        <v>17.03332266868216</v>
       </c>
       <c r="C3" t="n">
-        <v>47.1238898038469</v>
+        <v>44.6597030661874</v>
       </c>
       <c r="D3" t="n">
-        <v>64.62354263204629</v>
+        <v>80.96964190775569</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.25139383221197</v>
+        <v>28.39705234533899</v>
       </c>
       <c r="C4" t="n">
-        <v>93.9080949020244</v>
+        <v>86.42914089107219</v>
       </c>
       <c r="D4" t="n">
-        <v>76.78052445373456</v>
+        <v>120.7863835488936</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.16668579220627</v>
+        <v>42.28878236043136</v>
       </c>
       <c r="C5" t="n">
-        <v>153.2508166329271</v>
+        <v>144.5378057577367</v>
       </c>
       <c r="D5" t="n">
-        <v>61.08925089675779</v>
+        <v>95.45042054539616</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.46049039768332</v>
+        <v>46.73217246985243</v>
       </c>
       <c r="C6" t="n">
-        <v>216.6746635703838</v>
+        <v>200.3324912854914</v>
       </c>
       <c r="D6" t="n">
-        <v>47.49695393146069</v>
+        <v>63.67811959285662</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.01098881785852</v>
+        <v>37.42913122440964</v>
       </c>
       <c r="C7" t="n">
-        <v>226.7307053049838</v>
+        <v>224.9341070062122</v>
       </c>
       <c r="D7" t="n">
-        <v>41.50142070162541</v>
+        <v>45.75337000871835</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.45872252425729</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="C8" t="n">
-        <v>179.7481871705485</v>
+        <v>198.1903177948248</v>
       </c>
       <c r="D8" t="n">
-        <v>38.63668090063322</v>
+        <v>39.47116644924301</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.42031119060464</v>
+        <v>12.53593643552752</v>
       </c>
       <c r="C9" t="n">
-        <v>116.7062400900438</v>
+        <v>131.7937388089088</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>6.975317438673588</v>
       </c>
       <c r="C10" t="n">
-        <v>65.90963212460962</v>
+        <v>71.17670855789376</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
         <v>40.51476425885736</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.39843500367074</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.002538864047999</v>
+        <v>7.954156875288108</v>
       </c>
       <c r="C21" t="n">
-        <v>108.034274664648</v>
+        <v>106.3868482069784</v>
       </c>
       <c r="D21" t="n">
-        <v>11.003490938066</v>
+        <v>9.942696094110135</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.673340056393069</v>
+        <v>5.558655501445441</v>
       </c>
       <c r="C2" t="n">
-        <v>9.96277570269663</v>
+        <v>9.488591561545423</v>
       </c>
       <c r="D2" t="n">
-        <v>28.39705234533899</v>
+        <v>20.38697282638926</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.72745935331366</v>
+        <v>19.75276380944582</v>
       </c>
       <c r="C3" t="n">
-        <v>67.63259934556277</v>
+        <v>64.01976779393451</v>
       </c>
       <c r="D3" t="n">
-        <v>68.00566347317655</v>
+        <v>87.78297097522855</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.18160762975243</v>
+        <v>20.31825048709199</v>
       </c>
       <c r="C4" t="n">
-        <v>126.0829124133051</v>
+        <v>116.957567502331</v>
       </c>
       <c r="D4" t="n">
-        <v>72.0710807164626</v>
+        <v>112.4650900076976</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.67961575771283</v>
+        <v>26.31083847381452</v>
       </c>
       <c r="C5" t="n">
-        <v>129.4679784975481</v>
+        <v>119.6995888402924</v>
       </c>
       <c r="D5" t="n">
-        <v>44.79223900626073</v>
+        <v>62.78276568658354</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.18245050873644</v>
+        <v>23.2252054393668</v>
       </c>
       <c r="C6" t="n">
-        <v>149.3336432929823</v>
+        <v>148.1260936167588</v>
       </c>
       <c r="D6" t="n">
-        <v>27.33087433852696</v>
+        <v>30.10823859384119</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.18178755620168</v>
+        <v>15.57051858935441</v>
       </c>
       <c r="C7" t="n">
-        <v>126.360747013607</v>
+        <v>139.356141374722</v>
       </c>
       <c r="D7" t="n">
-        <v>27.12863431145211</v>
+        <v>27.72750041104266</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>85.95201150680825</v>
+        <v>97.13411785817941</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>26.20284622634736</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>50.25468323268996</v>
+        <v>54.35937038414588</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
         <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.18597658892593</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.952696183746906</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
         <v>17.47216389248049</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>71.95719798276996</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.540583132141498</v>
+        <v>3.463605900582747</v>
       </c>
       <c r="C2" t="n">
-        <v>4.979424355939822</v>
+        <v>4.760494617892784</v>
       </c>
       <c r="D2" t="n">
-        <v>21.10266690278519</v>
+        <v>14.27068462893163</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.94130042639022</v>
+        <v>19.89020848804038</v>
       </c>
       <c r="C3" t="n">
-        <v>54.33482669153972</v>
+        <v>51.78228266049802</v>
       </c>
       <c r="D3" t="n">
-        <v>73.66543898815942</v>
+        <v>84.6757394912874</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.97512181669111</v>
+        <v>27.32498385230147</v>
       </c>
       <c r="C4" t="n">
-        <v>150.7532504733232</v>
+        <v>140.8621423530366</v>
       </c>
       <c r="D4" t="n">
-        <v>86.33980184998573</v>
+        <v>127.8696932350343</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.64940256305943</v>
+        <v>29.28062527916113</v>
       </c>
       <c r="C5" t="n">
-        <v>177.450897542611</v>
+        <v>163.3382742940631</v>
       </c>
       <c r="D5" t="n">
-        <v>55.07604620824608</v>
+        <v>79.74245727744719</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.13340418125311</v>
+        <v>27.08936440328224</v>
       </c>
       <c r="C6" t="n">
-        <v>177.5903057166141</v>
+        <v>171.0292858091326</v>
       </c>
       <c r="D6" t="n">
-        <v>31.75855648468008</v>
+        <v>36.91076843656734</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.68462230722529</v>
+        <v>14.55244622005047</v>
       </c>
       <c r="C7" t="n">
-        <v>161.8136201093678</v>
+        <v>170.0180856737583</v>
       </c>
       <c r="D7" t="n">
-        <v>29.2845522699781</v>
+        <v>30.24273802932299</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>7.34347282776614</v>
       </c>
       <c r="C8" t="n">
-        <v>111.7376149588507</v>
+        <v>126.7583548338269</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.215624642035802</v>
       </c>
       <c r="C9" t="n">
-        <v>54.24843289356598</v>
+        <v>56.46718270516377</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>62.58837964114266</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.881830422591888</v>
+        <v>3.132756924251572</v>
       </c>
       <c r="C2" t="n">
-        <v>6.836891012374788</v>
+        <v>11.3421312271634</v>
       </c>
       <c r="D2" t="n">
-        <v>19.50241814486289</v>
+        <v>13.40871014460294</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.19455027635689</v>
+        <v>15.87486037767093</v>
       </c>
       <c r="C3" t="n">
-        <v>36.56028450615122</v>
+        <v>35.17602024316322</v>
       </c>
       <c r="D3" t="n">
-        <v>73.7488875430204</v>
+        <v>77.98512888684539</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.7220929509027</v>
+        <v>32.07271575003904</v>
       </c>
       <c r="C4" t="n">
-        <v>143.1466692608189</v>
+        <v>135.0551046824167</v>
       </c>
       <c r="D4" t="n">
-        <v>99.03870840441823</v>
+        <v>138.1564456801324</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.29445186247859</v>
+        <v>33.96847056693964</v>
       </c>
       <c r="C5" t="n">
-        <v>224.5011562686394</v>
+        <v>207.4187462147449</v>
       </c>
       <c r="D5" t="n">
-        <v>70.44039777970866</v>
+        <v>100.4573338370549</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.08435785376978</v>
+        <v>32.60384125803657</v>
       </c>
       <c r="C6" t="n">
-        <v>226.6570742271654</v>
+        <v>212.005471488986</v>
       </c>
       <c r="D6" t="n">
-        <v>39.7686360036298</v>
+        <v>49.91205328390785</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.12863431145211</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="C7" t="n">
-        <v>205.4709587695192</v>
+        <v>203.8540203006247</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.76762889372977</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>156.2156946997524</v>
+        <v>169.984706251814</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>87.97343002985241</v>
+        <v>96.51561680450389</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>45.55309347705201</v>
+        <v>46.6919208139783</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>14.46605242207675</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2579,7 +2579,7 @@
         <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.359139733305085</v>
+        <v>1.917353266394021</v>
       </c>
       <c r="C2" t="n">
-        <v>3.365431130158066</v>
+        <v>5.564545987670921</v>
       </c>
       <c r="D2" t="n">
-        <v>13.75330358879357</v>
+        <v>9.469938355164732</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.50241814486289</v>
+        <v>15.29562923216531</v>
       </c>
       <c r="C3" t="n">
-        <v>34.52806675836032</v>
+        <v>40.99287539082557</v>
       </c>
       <c r="D3" t="n">
-        <v>74.49501579824798</v>
+        <v>75.30986639277283</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.05316291141212</v>
+        <v>34.94432778496097</v>
       </c>
       <c r="C4" t="n">
-        <v>140.5047861886908</v>
+        <v>132.2345435281156</v>
       </c>
       <c r="D4" t="n">
-        <v>108.5979858006694</v>
+        <v>146.5415528221044</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.08614142272902</v>
+        <v>34.80295611554943</v>
       </c>
       <c r="C5" t="n">
-        <v>270.0787934382976</v>
+        <v>250.6401888942108</v>
       </c>
       <c r="D5" t="n">
-        <v>72.77204857729483</v>
+        <v>103.1816837163398</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.00006641992479</v>
+        <v>25.64030479181395</v>
       </c>
       <c r="C6" t="n">
-        <v>262.3200413316351</v>
+        <v>247.9099485287003</v>
       </c>
       <c r="D6" t="n">
-        <v>39.44662275663685</v>
+        <v>48.7850069194325</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.444012004226815</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>208.8844955371853</v>
+        <v>214.6934967032137</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>3.588287859022091</v>
       </c>
       <c r="C8" t="n">
-        <v>109.2341583130213</v>
+        <v>119.4148820060608</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>34.72343455150543</v>
+        <v>35.61093447614454</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>30.95155987178918</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.9964739198105126</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>19.19120412261664</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.56743447752142</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>14.53673825678252</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
         <v>12.18348900970292</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2876,7 +2876,7 @@
         <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.595740930028567</v>
+        <v>2.324778563656447</v>
       </c>
       <c r="C2" t="n">
-        <v>5.846307578789756</v>
+        <v>7.767587836000764</v>
       </c>
       <c r="D2" t="n">
-        <v>15.24850534236146</v>
+        <v>9.244136383187966</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.14698441819654</v>
+        <v>11.19683256693487</v>
       </c>
       <c r="C3" t="n">
-        <v>24.02827506144068</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D3" t="n">
-        <v>68.87451019143498</v>
+        <v>66.78829631991051</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.6282460819225</v>
+        <v>32.48112279500572</v>
       </c>
       <c r="C4" t="n">
-        <v>116.038651651156</v>
+        <v>118.1445004767654</v>
       </c>
       <c r="D4" t="n">
-        <v>118.361466719404</v>
+        <v>151.0595557570482</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.99550183876883</v>
+        <v>41.72427743048944</v>
       </c>
       <c r="C5" t="n">
-        <v>264.5073752166969</v>
+        <v>249.3639168786899</v>
       </c>
       <c r="D5" t="n">
-        <v>90.83620633543615</v>
+        <v>124.0438224315845</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.8151790563569</v>
+        <v>33.04660947265189</v>
       </c>
       <c r="C6" t="n">
-        <v>337.9529027191051</v>
+        <v>312.3931012390394</v>
       </c>
       <c r="D6" t="n">
-        <v>48.90576188705487</v>
+        <v>63.15484806649307</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.18745705824891</v>
+        <v>13.83380690054181</v>
       </c>
       <c r="C7" t="n">
-        <v>278.3529630896896</v>
+        <v>276.1970451311636</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>37.90822410408209</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>173.6564426656971</v>
+        <v>181.58405537749</v>
       </c>
       <c r="D8" t="n">
-        <v>32.71183350550372</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>69.22499412185107</v>
+        <v>72.44218134866787</v>
       </c>
       <c r="D9" t="n">
         <v>32.06093477758807</v>
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.9964739198105126</v>
       </c>
       <c r="C10" t="n">
         <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.05772749256809</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.21334235145782</v>
+      </c>
+      <c r="D14" t="n">
         <v>13.82791641431633</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
         <v>11.46681318560274</v>
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.777945092390974</v>
+        <v>1.519745446174062</v>
       </c>
       <c r="C2" t="n">
-        <v>4.963716392671873</v>
+        <v>4.612250714551515</v>
       </c>
       <c r="D2" t="n">
-        <v>12.13341987678633</v>
+        <v>8.22704576158827</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.10004045484194</v>
+        <v>9.935286766977722</v>
       </c>
       <c r="C3" t="n">
-        <v>23.89083038284613</v>
+        <v>31.61718481526853</v>
       </c>
       <c r="D3" t="n">
-        <v>66.06180301876786</v>
+        <v>60.95671495668446</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.77390459504952</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="C4" t="n">
-        <v>95.79697748499525</v>
+        <v>104.5777289517787</v>
       </c>
       <c r="D4" t="n">
-        <v>123.4665547814874</v>
+        <v>150.7277250330128</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.09429850399926</v>
+        <v>45.33220024359647</v>
       </c>
       <c r="C5" t="n">
-        <v>255.2544031041707</v>
+        <v>246.2959553029186</v>
       </c>
       <c r="D5" t="n">
-        <v>104.2616061910113</v>
+        <v>140.2181158590507</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.0944373727195</v>
+        <v>37.71580155404972</v>
       </c>
       <c r="C6" t="n">
-        <v>379.0900950224549</v>
+        <v>352.6447571131586</v>
       </c>
       <c r="D6" t="n">
-        <v>56.95609306187872</v>
+        <v>74.38506005537235</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.27108553955913</v>
+        <v>12.33664165156542</v>
       </c>
       <c r="C7" t="n">
-        <v>345.725399293627</v>
+        <v>335.6644488205056</v>
       </c>
       <c r="D7" t="n">
-        <v>38.50709020367265</v>
+        <v>42.63926629084747</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>3.67173641388307</v>
       </c>
       <c r="C8" t="n">
-        <v>219.7200449489574</v>
+        <v>227.1469663315845</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>73.32968127330699</v>
+        <v>76.54686850012379</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>21.85664913964673</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
         <v>19.7439280801076</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.44775906859456</v>
       </c>
       <c r="D14" t="n">
         <v>10.75504610002381</v>
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.595740930028567</v>
+        <v>1.968404147014855</v>
       </c>
       <c r="C2" t="n">
-        <v>4.923464736797754</v>
+        <v>11.93510684052847</v>
       </c>
       <c r="D2" t="n">
-        <v>16.03390350575891</v>
+        <v>10.92881544367549</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.321694451823465</v>
+        <v>7.736171909464865</v>
       </c>
       <c r="C3" t="n">
-        <v>21.8684301120977</v>
+        <v>25.4714441866835</v>
       </c>
       <c r="D3" t="n">
-        <v>61.33468782281948</v>
+        <v>54.92878405260904</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.86476516318797</v>
+        <v>24.35127005613788</v>
       </c>
       <c r="C4" t="n">
-        <v>80.54552689952106</v>
+        <v>93.5890268981442</v>
       </c>
       <c r="D4" t="n">
-        <v>126.197776894702</v>
+        <v>147.1796888298648</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.6525120370882</v>
+        <v>44.49771469498668</v>
       </c>
       <c r="C5" t="n">
-        <v>220.8932334555324</v>
+        <v>224.2557193425777</v>
       </c>
       <c r="D5" t="n">
-        <v>117.7115497391926</v>
+        <v>154.6252634188727</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.94980166502573</v>
+        <v>45.68562941712533</v>
       </c>
       <c r="C6" t="n">
-        <v>394.1844659752496</v>
+        <v>368.1013929688204</v>
       </c>
       <c r="D6" t="n">
-        <v>68.79007988886977</v>
+        <v>90.60647737264239</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.66761380108361</v>
+        <v>22.21793229480956</v>
       </c>
       <c r="C7" t="n">
-        <v>420.4040019125691</v>
+        <v>400.3419875762855</v>
       </c>
       <c r="D7" t="n">
-        <v>43.5375654402333</v>
+        <v>50.18497914568845</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.593818492349078</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>304.33687957799</v>
+        <v>307.0072333335413</v>
       </c>
       <c r="D8" t="n">
-        <v>35.21529015133309</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>140.4468630741401</v>
+        <v>142.7765503763178</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>49.11192890494669</v>
+        <v>50.25075624187299</v>
       </c>
       <c r="D10" t="n">
-        <v>26.05067533218912</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>12.22766765639403</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>10.75504610002381</v>
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.86005204664921</v>
+        <v>4.888121819444869</v>
       </c>
       <c r="C2" t="n">
-        <v>11.55517047898496</v>
+        <v>14.34038871593316</v>
       </c>
       <c r="D2" t="n">
-        <v>4.080143458849744</v>
+        <v>12.43677991739859</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.918335014098267</v>
+        <v>1.452986602285279</v>
       </c>
       <c r="C2" t="n">
-        <v>2.91480893390878</v>
+        <v>7.160867754776235</v>
       </c>
       <c r="D2" t="n">
-        <v>11.92921635430299</v>
+        <v>8.130834486572084</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.68418033886879</v>
+        <v>10.41143440353742</v>
       </c>
       <c r="C3" t="n">
-        <v>25.0247489812512</v>
+        <v>35.36255230697011</v>
       </c>
       <c r="D3" t="n">
-        <v>67.09754684674826</v>
+        <v>60.13695562363837</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.04490801915065</v>
+        <v>33.82120841130262</v>
       </c>
       <c r="C4" t="n">
-        <v>118.731585603905</v>
+        <v>132.7961032149448</v>
       </c>
       <c r="D4" t="n">
-        <v>126.7338111412208</v>
+        <v>150.0513008647868</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.51410130632262</v>
+        <v>25.72178985126644</v>
       </c>
       <c r="C5" t="n">
-        <v>333.3278892843983</v>
+        <v>320.3442758957343</v>
       </c>
       <c r="D5" t="n">
-        <v>104.5806741948915</v>
+        <v>137.4446785945535</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.14720540237479</v>
+        <v>13.76606630894878</v>
       </c>
       <c r="C6" t="n">
-        <v>342.5818431446288</v>
+        <v>324.9918695276387</v>
       </c>
       <c r="D6" t="n">
-        <v>58.24414604985053</v>
+        <v>72.57373554103698</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>214.0347439936641</v>
+        <v>215.8912289023948</v>
       </c>
       <c r="D7" t="n">
-        <v>29.88341836956866</v>
+        <v>30.18285141936394</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>103.4762080276138</v>
+        <v>105.2286276796944</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>24.11663235482289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.2218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>37.49687181600267</v>
+        <v>38.2734342500619</v>
       </c>
       <c r="D9" t="n">
-        <v>19.85781081380023</v>
+        <v>19.41406085148067</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>18.64829764216817</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>14.39340309196248</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>9.980447161373073</v>
       </c>
       <c r="D12" t="n">
         <v>13.0179745583127</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
         <v>8.845546815263763</v>
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.723990026386404</v>
+        <v>5.6018524004323</v>
       </c>
       <c r="C2" t="n">
-        <v>6.468735623282234</v>
+        <v>9.064476553310801</v>
       </c>
       <c r="D2" t="n">
-        <v>5.950372835439918</v>
+        <v>14.39634833507523</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.44856088984956</v>
+        <v>10.38689071093125</v>
       </c>
       <c r="C3" t="n">
-        <v>29.11863690796039</v>
+        <v>36.13322425480386</v>
       </c>
       <c r="D3" t="n">
-        <v>6.562983402889927</v>
+        <v>13.58247948825462</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39831182476694</v>
+        <v>13.39656851974029</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14410308260341</v>
+        <v>70.13497636805212</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576271979384346</v>
+        <v>1.576066884675328</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.391758391723482</v>
+        <v>3.684499134038279</v>
       </c>
       <c r="C2" t="n">
-        <v>6.66999390265283</v>
+        <v>6.365652114336318</v>
       </c>
       <c r="D2" t="n">
-        <v>13.37042198413731</v>
+        <v>18.63553492201295</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.9133695223148</v>
+        <v>15.76195939168254</v>
       </c>
       <c r="C3" t="n">
-        <v>26.6839026014283</v>
+        <v>35.64235040268045</v>
       </c>
       <c r="D3" t="n">
-        <v>9.974556675147594</v>
+        <v>22.39366513386975</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.48568737616169</v>
+        <v>12.16287230791373</v>
       </c>
       <c r="C4" t="n">
-        <v>44.88648678586841</v>
+        <v>55.59440899608838</v>
       </c>
       <c r="D4" t="n">
-        <v>18.50594422505237</v>
+        <v>22.19437034990764</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44175864368577</v>
+        <v>15.4357455417586</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14875874898378</v>
+        <v>86.11521196981113</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250896556565426</v>
+        <v>3.249630640370231</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.05698242457532</v>
+        <v>4.606360228326034</v>
       </c>
       <c r="C2" t="n">
-        <v>8.994772466309277</v>
+        <v>9.993209881528283</v>
       </c>
       <c r="D2" t="n">
-        <v>15.15229406734527</v>
+        <v>20.91711658668254</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.78574232076272</v>
+        <v>14.05371838629309</v>
       </c>
       <c r="C3" t="n">
-        <v>26.24211613451724</v>
+        <v>29.13827186204533</v>
       </c>
       <c r="D3" t="n">
-        <v>18.35377333089412</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.0697294491973</v>
+        <v>22.24542123052848</v>
       </c>
       <c r="C4" t="n">
-        <v>57.81512230309466</v>
+        <v>75.0703199529366</v>
       </c>
       <c r="D4" t="n">
-        <v>19.36104647545135</v>
+        <v>28.43534050580462</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.66454538478386</v>
+        <v>10.92194320974577</v>
       </c>
       <c r="C5" t="n">
-        <v>49.55371537185777</v>
+        <v>59.8375225738431</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>30.92505268377453</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.78845088416398</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73455514787586</v>
+        <v>16.72188819196585</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0807864020427</v>
+        <v>102.0035179709917</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020366544362757</v>
+        <v>4.180472047991462</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.432991795301848</v>
+        <v>5.772676500971245</v>
       </c>
       <c r="C2" t="n">
-        <v>11.51884581392783</v>
+        <v>6.915430828714532</v>
       </c>
       <c r="D2" t="n">
-        <v>17.35533591567511</v>
+        <v>29.79211583307371</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.14760631300229</v>
+        <v>14.93729132011522</v>
       </c>
       <c r="C3" t="n">
-        <v>31.22939447209104</v>
+        <v>34.57224540505143</v>
       </c>
       <c r="D3" t="n">
-        <v>25.78560345204247</v>
+        <v>40.86033945075225</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.81746134693488</v>
+        <v>24.92559246312227</v>
       </c>
       <c r="C4" t="n">
-        <v>62.2054980364864</v>
+        <v>73.87062425834699</v>
       </c>
       <c r="D4" t="n">
-        <v>23.94286301117121</v>
+        <v>37.59897357724434</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.50718801466389</v>
+        <v>21.77025534167302</v>
       </c>
       <c r="C5" t="n">
-        <v>80.45422436302613</v>
+        <v>101.0218387669968</v>
       </c>
       <c r="D5" t="n">
-        <v>29.32971266437347</v>
+        <v>34.06664533736433</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.63272854762046</v>
+        <v>10.30442390377452</v>
       </c>
       <c r="C6" t="n">
-        <v>46.36990756698535</v>
+        <v>55.02401357992099</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>37.63529824230149</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="D7" t="n">
         <v>39.76470901281281</v>
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.2097595180061</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,7 +5557,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
         <v>33.31069960509428</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05805012735702</v>
+        <v>18.03505418246903</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8072794022815</v>
+        <v>117.6572582380123</v>
       </c>
       <c r="D21" t="n">
-        <v>6.879257191374101</v>
+        <v>6.011684727489678</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.373105185342792</v>
+        <v>5.454590244795278</v>
       </c>
       <c r="C2" t="n">
-        <v>12.26399232145116</v>
+        <v>10.45757654563702</v>
       </c>
       <c r="D2" t="n">
-        <v>18.42151392248715</v>
+        <v>35.84066343893831</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.38046044535803</v>
+        <v>15.60487975900305</v>
       </c>
       <c r="C3" t="n">
-        <v>36.61918936840603</v>
+        <v>28.36759991421159</v>
       </c>
       <c r="D3" t="n">
-        <v>31.26866438026091</v>
+        <v>50.36856596638261</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.5299481383108</v>
+        <v>19.65458903902115</v>
       </c>
       <c r="C4" t="n">
-        <v>59.52532680389261</v>
+        <v>66.76178913189584</v>
       </c>
       <c r="D4" t="n">
-        <v>27.10801760966293</v>
+        <v>41.77238306799753</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.60474089028281</v>
+        <v>17.86780821729195</v>
       </c>
       <c r="C5" t="n">
-        <v>73.50835935547994</v>
+        <v>88.82362354173019</v>
       </c>
       <c r="D5" t="n">
-        <v>25.13274122871835</v>
+        <v>32.10314992887071</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.92078153559227</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C6" t="n">
-        <v>59.37119241432587</v>
+        <v>72.73474216453346</v>
       </c>
       <c r="D6" t="n">
-        <v>30.22899356146354</v>
+        <v>30.5510068084565</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>28.44613973055133</v>
+        <v>32.09922293805371</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
         <v>19.96089432274615</v>
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.055996145122117</v>
+        <v>7.042226314307506</v>
       </c>
       <c r="C21" t="n">
-        <v>66.14996386051985</v>
+        <v>66.02087169663287</v>
       </c>
       <c r="D21" t="n">
-        <v>5.291997108841588</v>
+        <v>4.401391446442191</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.944081438586937</v>
+        <v>4.379576508645021</v>
       </c>
       <c r="C2" t="n">
-        <v>6.080945280104743</v>
+        <v>8.130834486572084</v>
       </c>
       <c r="D2" t="n">
-        <v>16.58171872472863</v>
+        <v>34.27870284148163</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.87271695581319</v>
+        <v>17.64200624531518</v>
       </c>
       <c r="C3" t="n">
-        <v>43.90866607243859</v>
+        <v>36.13322425480386</v>
       </c>
       <c r="D3" t="n">
-        <v>39.18645961501144</v>
+        <v>68.30509652297182</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.09900195387546</v>
+        <v>26.16357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>79.86910273129502</v>
+        <v>69.46748580480005</v>
       </c>
       <c r="D4" t="n">
-        <v>36.94807484932871</v>
+        <v>58.47878375116551</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.14594591723007</v>
+        <v>24.3473430653209</v>
       </c>
       <c r="C5" t="n">
-        <v>95.96583809012573</v>
+        <v>108.5322087044849</v>
       </c>
       <c r="D5" t="n">
-        <v>29.7960428238907</v>
+        <v>40.37437433715008</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.98369550412208</v>
+        <v>18.31450342272425</v>
       </c>
       <c r="C6" t="n">
-        <v>93.26308666033425</v>
+        <v>112.4631265122891</v>
       </c>
       <c r="D6" t="n">
-        <v>31.87931145230244</v>
+        <v>33.85164259013428</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.31856928226148</v>
+        <v>9.402197763571703</v>
       </c>
       <c r="C7" t="n">
-        <v>61.86286808770426</v>
+        <v>73.84019007951534</v>
       </c>
       <c r="D7" t="n">
-        <v>32.81786225756237</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>32.29459073119883</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.07499804061703</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6207,7 +6207,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
         <v>22.1305567491316</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.276669185086543</v>
+        <v>7.256144332522489</v>
       </c>
       <c r="C21" t="n">
-        <v>75.49544279527288</v>
+        <v>75.28249744992084</v>
       </c>
       <c r="D21" t="n">
-        <v>6.367085536950724</v>
+        <v>5.442108249391867</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.868486865359933</v>
+        <v>4.342270095883642</v>
       </c>
       <c r="C2" t="n">
-        <v>8.744426801726341</v>
+        <v>9.802750826904402</v>
       </c>
       <c r="D2" t="n">
-        <v>24.01649408898972</v>
+        <v>29.46421209985527</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.60764507566654</v>
+        <v>16.19883712007237</v>
       </c>
       <c r="C3" t="n">
-        <v>31.80862561759665</v>
+        <v>33.472687976295</v>
       </c>
       <c r="D3" t="n">
-        <v>43.35888735806038</v>
+        <v>79.16322613194156</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.13652935081509</v>
+        <v>30.61776565234527</v>
       </c>
       <c r="C4" t="n">
-        <v>97.29021574315466</v>
+        <v>80.50723873905544</v>
       </c>
       <c r="D4" t="n">
-        <v>48.28137034715389</v>
+        <v>77.86535566692727</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.2145293878071</v>
+        <v>31.88225669541517</v>
       </c>
       <c r="C5" t="n">
-        <v>124.0192787389783</v>
+        <v>119.503239299443</v>
       </c>
       <c r="D5" t="n">
-        <v>36.12831551628263</v>
+        <v>52.27806525114266</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.12711278440013</v>
+        <v>25.84156307118455</v>
       </c>
       <c r="C6" t="n">
-        <v>126.0279345418673</v>
+        <v>144.5436962439622</v>
       </c>
       <c r="D6" t="n">
-        <v>34.49566908412018</v>
+        <v>38.96360288614742</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.94224111636546</v>
+        <v>15.92983824910874</v>
       </c>
       <c r="C7" t="n">
-        <v>101.7473503204352</v>
+        <v>119.7732199181109</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>57.57950285407543</v>
+        <v>66.84229244364408</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>31.06249736236907</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>18.82992096745382</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.483323584886019</v>
+        <v>7.454964220698987</v>
       </c>
       <c r="C21" t="n">
-        <v>84.18739032996771</v>
+        <v>83.8683474828636</v>
       </c>
       <c r="D21" t="n">
-        <v>7.483323584886019</v>
+        <v>6.523093693111614</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_67_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_67_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497645002496</v>
+        <v>10.8449764967193</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907235241539</v>
+        <v>37.78907251512077</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.654465865834128</v>
+        <v>0.9228428419920017</v>
       </c>
       <c r="C2" t="n">
-        <v>9.81256830394687</v>
+        <v>2.919717672430014</v>
       </c>
       <c r="D2" t="n">
-        <v>24.86766934857171</v>
+        <v>14.8803499532689</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.33489914033518</v>
+        <v>6.05738333520282</v>
       </c>
       <c r="C3" t="n">
-        <v>35.74052517310513</v>
+        <v>34.13045893814036</v>
       </c>
       <c r="D3" t="n">
-        <v>83.10985190301373</v>
+        <v>79.84554078639309</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.8092064546734</v>
+        <v>10.35056604587412</v>
       </c>
       <c r="C4" t="n">
-        <v>81.24747650805753</v>
+        <v>93.89533218186919</v>
       </c>
       <c r="D4" t="n">
-        <v>95.63106212297755</v>
+        <v>94.91634979428588</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.23907308041327</v>
+        <v>11.46190444708151</v>
       </c>
       <c r="C5" t="n">
-        <v>133.9594742444773</v>
+        <v>107.1577619185394</v>
       </c>
       <c r="D5" t="n">
-        <v>66.58703804053992</v>
+        <v>55.61600744558182</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.85164259013428</v>
+        <v>8.573602701187397</v>
       </c>
       <c r="C6" t="n">
-        <v>165.3538023308818</v>
+        <v>71.80895407942872</v>
       </c>
       <c r="D6" t="n">
-        <v>45.24286120251001</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.1162314441954</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>163.6102184081394</v>
+        <v>40.42346172236242</v>
       </c>
       <c r="D7" t="n">
-        <v>38.62686342359076</v>
+        <v>29.40432548989622</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.2669375645639</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>110.2355409713531</v>
+        <v>28.87319998189869</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>56.68905768632355</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.637722181383358</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91.65266617660029</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.637722181383358</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.14377713317654</v>
+        <v>0.7363107781851078</v>
       </c>
       <c r="C2" t="n">
-        <v>14.44543572028757</v>
+        <v>3.272165098254619</v>
       </c>
       <c r="D2" t="n">
-        <v>22.32494279457247</v>
+        <v>23.33614292994668</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.22690689286803</v>
+        <v>4.5553093477052</v>
       </c>
       <c r="C3" t="n">
-        <v>36.62900684544849</v>
+        <v>20.86213871524472</v>
       </c>
       <c r="D3" t="n">
-        <v>82.93313731624932</v>
+        <v>73.98941573056086</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.52017171899734</v>
+        <v>11.10356653503143</v>
       </c>
       <c r="C4" t="n">
-        <v>84.82103815151592</v>
+        <v>89.10931212366599</v>
       </c>
       <c r="D4" t="n">
-        <v>111.2143434324872</v>
+        <v>112.5799544890945</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.77336481570179</v>
+        <v>13.79355524466769</v>
       </c>
       <c r="C5" t="n">
-        <v>139.5063487734718</v>
+        <v>144.7096116059799</v>
       </c>
       <c r="D5" t="n">
-        <v>80.79783605951251</v>
+        <v>75.84001015306612</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.17744395922398</v>
+        <v>11.91449013873929</v>
       </c>
       <c r="C6" t="n">
-        <v>185.1576170209485</v>
+        <v>123.6128351894202</v>
       </c>
       <c r="D6" t="n">
-        <v>53.81646390369741</v>
+        <v>39.92964262712628</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.3625112492411</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>198.2246789644735</v>
+        <v>72.64245788033423</v>
       </c>
       <c r="D7" t="n">
-        <v>41.74096714146164</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.69109363052752</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>156.3825918094744</v>
+        <v>41.47393176590651</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>32.54493639578176</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.207811718130833</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>91.85624220014853</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61249706092553</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.836490101747287</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>46.97662764820988</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.804251819638826</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99.50421070039503</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.77978329709368</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.925829142833748</v>
+        <v>0.3877903431774901</v>
       </c>
       <c r="C2" t="n">
-        <v>13.47841423160446</v>
+        <v>1.382300767579509</v>
       </c>
       <c r="D2" t="n">
-        <v>24.31789063419349</v>
+        <v>15.70403627713198</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.03332266868216</v>
+        <v>4.14297531192154</v>
       </c>
       <c r="C3" t="n">
-        <v>44.6597030661874</v>
+        <v>18.22614612934204</v>
       </c>
       <c r="D3" t="n">
-        <v>80.96964190775569</v>
+        <v>77.4402589109884</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.39705234533899</v>
+        <v>12.36707583039707</v>
       </c>
       <c r="C4" t="n">
-        <v>86.42914089107219</v>
+        <v>82.93215556854506</v>
       </c>
       <c r="D4" t="n">
-        <v>120.7863835488936</v>
+        <v>124.8321658380947</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.28878236043136</v>
+        <v>14.23534171157875</v>
       </c>
       <c r="C5" t="n">
-        <v>144.5378057577367</v>
+        <v>168.2961002005095</v>
       </c>
       <c r="D5" t="n">
-        <v>95.45042054539616</v>
+        <v>85.338419191654</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.73217246985243</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>200.3324912854914</v>
+        <v>161.368888399344</v>
       </c>
       <c r="D6" t="n">
-        <v>63.67811959285662</v>
+        <v>40.37241084174159</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.42913122440964</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>224.9341070062122</v>
+        <v>70.60631314172635</v>
       </c>
       <c r="D7" t="n">
-        <v>45.75337000871835</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.53249247079604</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>198.1903177948248</v>
+        <v>40.55599766243574</v>
       </c>
       <c r="D8" t="n">
-        <v>39.47116644924301</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.53593643552752</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>131.7937388089088</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.975317438673588</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>71.17670855789376</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>40.51476425885736</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.39843500367074</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.954156875288108</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>106.3868482069784</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.942696094110135</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.558655501445441</v>
+        <v>0.3495021827118645</v>
       </c>
       <c r="C2" t="n">
-        <v>9.488591561545423</v>
+        <v>6.662139921018856</v>
       </c>
       <c r="D2" t="n">
-        <v>20.38697282638926</v>
+        <v>13.86424107937346</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.75276380944582</v>
+        <v>2.68998870963626</v>
       </c>
       <c r="C3" t="n">
-        <v>64.01976779393451</v>
+        <v>10.96612185643687</v>
       </c>
       <c r="D3" t="n">
-        <v>87.78297097522855</v>
+        <v>72.89476704032568</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.31825048709199</v>
+        <v>10.35056604587412</v>
       </c>
       <c r="C4" t="n">
-        <v>116.957567502331</v>
+        <v>63.22651564890308</v>
       </c>
       <c r="D4" t="n">
-        <v>112.4650900076976</v>
+        <v>134.2510533126386</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.31083847381452</v>
+        <v>16.51790512395259</v>
       </c>
       <c r="C5" t="n">
-        <v>119.6995888402924</v>
+        <v>161.9883712007237</v>
       </c>
       <c r="D5" t="n">
-        <v>62.78276568658354</v>
+        <v>107.9922474671492</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.2252054393668</v>
+        <v>14.28933783531233</v>
       </c>
       <c r="C6" t="n">
-        <v>148.1260936167588</v>
+        <v>216.7954185380062</v>
       </c>
       <c r="D6" t="n">
-        <v>30.10823859384119</v>
+        <v>55.50703345041042</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.57051858935441</v>
+        <v>7.306166415004762</v>
       </c>
       <c r="C7" t="n">
-        <v>139.356141374722</v>
+        <v>146.6623077897268</v>
       </c>
       <c r="D7" t="n">
-        <v>27.72750041104266</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>97.13411785817941</v>
+        <v>64.50573290753667</v>
       </c>
       <c r="D8" t="n">
-        <v>26.20284622634736</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>54.35937038414588</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>28.18597658892593</v>
+        <v>31.8871654339364</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
+        <v>24.00864010735575</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.5585576904542</v>
-      </c>
-      <c r="D15" t="n">
-        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.463605900582747</v>
+        <v>0.2130392518215578</v>
       </c>
       <c r="C2" t="n">
-        <v>4.760494617892784</v>
+        <v>3.449861432723292</v>
       </c>
       <c r="D2" t="n">
-        <v>14.27068462893163</v>
+        <v>10.3584200275081</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.89020848804038</v>
+        <v>2.0469439633546</v>
       </c>
       <c r="C3" t="n">
-        <v>51.78228266049802</v>
+        <v>18.95754816900591</v>
       </c>
       <c r="D3" t="n">
-        <v>84.6757394912874</v>
+        <v>68.20692175254715</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.32498385230147</v>
+        <v>8.423395302437632</v>
       </c>
       <c r="C4" t="n">
-        <v>140.8621423530366</v>
+        <v>47.40074265644449</v>
       </c>
       <c r="D4" t="n">
-        <v>127.8696932350343</v>
+        <v>139.9432265018616</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.28062527916113</v>
+        <v>17.25421590213769</v>
       </c>
       <c r="C5" t="n">
-        <v>163.3382742940631</v>
+        <v>147.753029489145</v>
       </c>
       <c r="D5" t="n">
-        <v>79.74245727744719</v>
+        <v>126.9645218517188</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.08936440328224</v>
+        <v>17.22770871412303</v>
       </c>
       <c r="C6" t="n">
-        <v>171.0292858091326</v>
+        <v>245.6156041438756</v>
       </c>
       <c r="D6" t="n">
-        <v>36.91076843656734</v>
+        <v>69.2730997593592</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.55244622005047</v>
+        <v>8.144578954431539</v>
       </c>
       <c r="C7" t="n">
-        <v>170.0180856737583</v>
+        <v>208.3455160475538</v>
       </c>
       <c r="D7" t="n">
-        <v>30.24273802932299</v>
+        <v>40.78278138211675</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.34347282776614</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>126.7583548338269</v>
+        <v>99.5541259491478</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.215624642035802</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>56.46718270516377</v>
+        <v>48.03593342109217</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.421570675749381</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>62.58837964114266</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.132756924251572</v>
+        <v>0.3897538385859837</v>
       </c>
       <c r="C2" t="n">
-        <v>11.3421312271634</v>
+        <v>5.582217446347364</v>
       </c>
       <c r="D2" t="n">
-        <v>13.40871014460294</v>
+        <v>12.466232348526</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.87486037767093</v>
+        <v>1.384264262988003</v>
       </c>
       <c r="C3" t="n">
-        <v>35.17602024316322</v>
+        <v>15.95340019401067</v>
       </c>
       <c r="D3" t="n">
-        <v>77.98512888684539</v>
+        <v>61.38868394655306</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.07271575003904</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="C4" t="n">
-        <v>135.0551046824167</v>
+        <v>47.78362426110075</v>
       </c>
       <c r="D4" t="n">
-        <v>138.1564456801324</v>
+        <v>141.7810582042116</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.96847056693964</v>
+        <v>15.58524480491812</v>
       </c>
       <c r="C5" t="n">
-        <v>207.4187462147449</v>
+        <v>118.5951226730147</v>
       </c>
       <c r="D5" t="n">
-        <v>100.4573338370549</v>
+        <v>144.9305048394354</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.60384125803657</v>
+        <v>20.04532462531138</v>
       </c>
       <c r="C6" t="n">
-        <v>212.005471488986</v>
+        <v>241.7916968358342</v>
       </c>
       <c r="D6" t="n">
-        <v>49.91205328390785</v>
+        <v>88.35238464369172</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.9603134856694</v>
+        <v>13.11516758103314</v>
       </c>
       <c r="C7" t="n">
-        <v>203.8540203006247</v>
+        <v>277.9936434299353</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>48.86747372658923</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>169.984706251814</v>
+        <v>177.0778334149972</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>41.97462309507237</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>96.51561680450389</v>
+        <v>79.87499321752047</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>42.48905889209769</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>46.6919208139783</v>
+        <v>42.84837855185204</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.421570675749381</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.95125677215293</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.917353266394021</v>
+        <v>0.2611448893296516</v>
       </c>
       <c r="C2" t="n">
-        <v>5.564545987670921</v>
+        <v>2.902046213753571</v>
       </c>
       <c r="D2" t="n">
-        <v>9.469938355164732</v>
+        <v>8.975137512224341</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.29562923216531</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C3" t="n">
-        <v>40.99287539082557</v>
+        <v>20.52343575727957</v>
       </c>
       <c r="D3" t="n">
-        <v>75.30986639277283</v>
+        <v>66.53304191680634</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.94432778496097</v>
+        <v>10.49095596758142</v>
       </c>
       <c r="C4" t="n">
-        <v>132.2345435281156</v>
+        <v>68.62514627455629</v>
       </c>
       <c r="D4" t="n">
-        <v>146.5415528221044</v>
+        <v>145.9417049748096</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.80295611554943</v>
+        <v>12.44365215132832</v>
       </c>
       <c r="C5" t="n">
-        <v>250.6401888942108</v>
+        <v>191.4653460207342</v>
       </c>
       <c r="D5" t="n">
-        <v>103.1816837163398</v>
+        <v>132.4623089955009</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.64030479181395</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>247.9099485287003</v>
+        <v>242.3149683621978</v>
       </c>
       <c r="D6" t="n">
-        <v>48.7850069194325</v>
+        <v>72.37247726166638</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.767186925373263</v>
+        <v>3.892629647338603</v>
       </c>
       <c r="C7" t="n">
-        <v>214.6934967032137</v>
+        <v>124.5042621048762</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.588287859022091</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>119.4148820060608</v>
+        <v>58.83123117699011</v>
       </c>
       <c r="D8" t="n">
-        <v>30.29182541453534</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>35.61093447614454</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9964739198105126</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.19120412261664</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>22.56743447752142</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.53673825678252</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.46681318560274</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.324778563656447</v>
+        <v>0.1992947839621025</v>
       </c>
       <c r="C2" t="n">
-        <v>7.767587836000764</v>
+        <v>2.243293504203962</v>
       </c>
       <c r="D2" t="n">
-        <v>9.244136383187966</v>
+        <v>6.918376071827272</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.19683256693487</v>
+        <v>1.47753029489145</v>
       </c>
       <c r="C3" t="n">
-        <v>31.71045084717197</v>
+        <v>15.47725255745097</v>
       </c>
       <c r="D3" t="n">
-        <v>66.78829631991051</v>
+        <v>58.64469911318322</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.48112279500572</v>
+        <v>6.840818003191774</v>
       </c>
       <c r="C4" t="n">
-        <v>118.1445004767654</v>
+        <v>57.70025782169779</v>
       </c>
       <c r="D4" t="n">
-        <v>151.0595557570482</v>
+        <v>140.1729554646554</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.72427743048944</v>
+        <v>11.31464229144449</v>
       </c>
       <c r="C5" t="n">
-        <v>249.3639168786899</v>
+        <v>143.6051454387022</v>
       </c>
       <c r="D5" t="n">
-        <v>124.0438224315845</v>
+        <v>138.524601069225</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.04660947265189</v>
+        <v>7.728317927830893</v>
       </c>
       <c r="C6" t="n">
-        <v>312.3931012390394</v>
+        <v>227.1803457535289</v>
       </c>
       <c r="D6" t="n">
-        <v>63.15484806649307</v>
+        <v>77.80645080467248</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.83380690054181</v>
+        <v>3.173990327829938</v>
       </c>
       <c r="C7" t="n">
-        <v>276.1970451311636</v>
+        <v>162.4723728189174</v>
       </c>
       <c r="D7" t="n">
-        <v>37.90822410408209</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>181.58405537749</v>
+        <v>67.176086663088</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>72.44218134866787</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>21.63281066307846</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9964739198105126</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>18.64829764216817</v>
       </c>
       <c r="D10" t="n">
-        <v>24.05772749256809</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.519745446174062</v>
+        <v>0.3141592653589793</v>
       </c>
       <c r="C2" t="n">
-        <v>4.612250714551515</v>
+        <v>9.438522428628835</v>
       </c>
       <c r="D2" t="n">
-        <v>8.22704576158827</v>
+        <v>11.51295532770235</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.935286766977722</v>
+        <v>1.040652566501619</v>
       </c>
       <c r="C3" t="n">
-        <v>31.61718481526853</v>
+        <v>11.38336463074177</v>
       </c>
       <c r="D3" t="n">
-        <v>60.95671495668446</v>
+        <v>50.5698242457532</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.07347651356504</v>
+        <v>4.773257338047992</v>
       </c>
       <c r="C4" t="n">
-        <v>104.5777289517787</v>
+        <v>47.15825097349554</v>
       </c>
       <c r="D4" t="n">
-        <v>150.7277250330128</v>
+        <v>138.2713101615293</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.33220024359647</v>
+        <v>10.99557428756428</v>
       </c>
       <c r="C5" t="n">
-        <v>246.2959553029186</v>
+        <v>123.0620747273377</v>
       </c>
       <c r="D5" t="n">
-        <v>140.2181158590507</v>
+        <v>158.2086425393735</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.71580155404972</v>
+        <v>11.63272854762046</v>
       </c>
       <c r="C6" t="n">
-        <v>352.6447571131586</v>
+        <v>231.1652596850668</v>
       </c>
       <c r="D6" t="n">
-        <v>74.38506005537235</v>
+        <v>102.5209675113817</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.33664165156542</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>335.6644488205056</v>
+        <v>251.70342165791</v>
       </c>
       <c r="D7" t="n">
-        <v>42.63926629084747</v>
+        <v>49.10702016642545</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.67173641388307</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>227.1469663315845</v>
+        <v>142.6970288122739</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.442187377538564</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>76.54686850012379</v>
+        <v>56.68905768632355</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>23.62968549351647</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.85664913964673</v>
+        <v>17.41424077792992</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.44775906859456</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.968404147014855</v>
+        <v>0.6273367830137118</v>
       </c>
       <c r="C2" t="n">
-        <v>11.93510684052847</v>
+        <v>8.606982123131786</v>
       </c>
       <c r="D2" t="n">
-        <v>10.92881544367549</v>
+        <v>11.70537787773472</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.736171909464865</v>
+        <v>1.050470043544087</v>
       </c>
       <c r="C3" t="n">
-        <v>25.4714441866835</v>
+        <v>25.41253932442869</v>
       </c>
       <c r="D3" t="n">
-        <v>54.92878405260904</v>
+        <v>48.09582003105124</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.35127005613788</v>
+        <v>3.343832680664637</v>
       </c>
       <c r="C4" t="n">
-        <v>93.5890268981442</v>
+        <v>37.06293933072559</v>
       </c>
       <c r="D4" t="n">
-        <v>147.1796888298648</v>
+        <v>131.5581193598896</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.49771469498668</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="C5" t="n">
-        <v>224.2557193425777</v>
+        <v>104.3352372688298</v>
       </c>
       <c r="D5" t="n">
-        <v>154.6252634188727</v>
+        <v>172.0021977840412</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.68562941712533</v>
+        <v>13.36354975020759</v>
       </c>
       <c r="C6" t="n">
-        <v>368.1013929688204</v>
+        <v>214.6620807766779</v>
       </c>
       <c r="D6" t="n">
-        <v>90.60647737264239</v>
+        <v>126.7122126917273</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.21793229480956</v>
+        <v>9.761517423326035</v>
       </c>
       <c r="C7" t="n">
-        <v>400.3419875762855</v>
+        <v>294.941554048348</v>
       </c>
       <c r="D7" t="n">
-        <v>50.18497914568845</v>
+        <v>64.31821909602553</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>307.0072333335413</v>
+        <v>236.4097559211531</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>142.7765503763178</v>
+        <v>113.9328028255466</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>25.73749781453438</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>50.25075624187299</v>
+        <v>45.83780031128358</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.22766765639403</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>25.62557857625024</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.888121819444869</v>
+        <v>2.488730430265664</v>
       </c>
       <c r="C2" t="n">
-        <v>14.34038871593316</v>
+        <v>8.551022503989719</v>
       </c>
       <c r="D2" t="n">
-        <v>12.43677991739859</v>
+        <v>16.88017002681966</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.452986602285279</v>
+        <v>0.5900303702523331</v>
       </c>
       <c r="C2" t="n">
-        <v>7.160867754776235</v>
+        <v>15.61666073145401</v>
       </c>
       <c r="D2" t="n">
-        <v>8.130834486572084</v>
+        <v>16.929257412032</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.41143440353742</v>
+        <v>1.556070111231195</v>
       </c>
       <c r="C3" t="n">
-        <v>35.36255230697011</v>
+        <v>29.31007771028852</v>
       </c>
       <c r="D3" t="n">
-        <v>60.13695562363837</v>
+        <v>46.27958677819464</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.82120841130262</v>
+        <v>2.680171232593792</v>
       </c>
       <c r="C4" t="n">
-        <v>132.7961032149448</v>
+        <v>49.92776124717579</v>
       </c>
       <c r="D4" t="n">
-        <v>150.0513008647868</v>
+        <v>126.4913194582718</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.72178985126644</v>
+        <v>7.485826244881931</v>
       </c>
       <c r="C5" t="n">
-        <v>320.3442758957343</v>
+        <v>86.24653581808231</v>
       </c>
       <c r="D5" t="n">
-        <v>137.4446785945535</v>
+        <v>179.1934997176491</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.76606630894878</v>
+        <v>13.28304643845935</v>
       </c>
       <c r="C6" t="n">
-        <v>324.9918695276387</v>
+        <v>193.3287031633947</v>
       </c>
       <c r="D6" t="n">
-        <v>72.57373554103698</v>
+        <v>146.1537624789269</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.19206269713388</v>
+        <v>12.45641487148353</v>
       </c>
       <c r="C7" t="n">
-        <v>215.8912289023948</v>
+        <v>305.3019375712646</v>
       </c>
       <c r="D7" t="n">
-        <v>30.18285141936394</v>
+        <v>81.86499581402876</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.251728322914683</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>105.2286276796944</v>
+        <v>305.8389535654876</v>
       </c>
       <c r="D8" t="n">
-        <v>24.11663235482289</v>
+        <v>42.47531442423825</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2218749811597791</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>38.2734342500619</v>
+        <v>194.3624834959665</v>
       </c>
       <c r="D9" t="n">
-        <v>19.41406085148067</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>84.13086951543042</v>
       </c>
       <c r="D10" t="n">
-        <v>18.64829764216817</v>
+        <v>22.63419332141022</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.39340309196248</v>
+        <v>35.53926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.72429312602266</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>9.980447161373073</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.6018524004323</v>
+        <v>3.50582105186536</v>
       </c>
       <c r="C2" t="n">
-        <v>9.064476553310801</v>
+        <v>8.357618206253097</v>
       </c>
       <c r="D2" t="n">
-        <v>14.39634833507523</v>
+        <v>21.5915772595001</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.38689071093125</v>
+        <v>4.123340357836604</v>
       </c>
       <c r="C3" t="n">
-        <v>36.13322425480386</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D3" t="n">
-        <v>13.58247948825462</v>
+        <v>14.49550485320416</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39656851974029</v>
+        <v>11.67754797031116</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13497636805212</v>
+        <v>59.94474624759732</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576066884675328</v>
+        <v>0.7785031980207443</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.684499134038279</v>
+        <v>1.86826588118168</v>
       </c>
       <c r="C2" t="n">
-        <v>6.365652114336318</v>
+        <v>6.187955779867646</v>
       </c>
       <c r="D2" t="n">
-        <v>18.63553492201295</v>
+        <v>26.15670408424777</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.76195939168254</v>
+        <v>9.184249773228911</v>
       </c>
       <c r="C3" t="n">
-        <v>35.64235040268045</v>
+        <v>27.40057842552848</v>
       </c>
       <c r="D3" t="n">
-        <v>22.39366513386975</v>
+        <v>29.85003894762427</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.16287230791373</v>
+        <v>5.296528864411542</v>
       </c>
       <c r="C4" t="n">
-        <v>55.59440899608838</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D4" t="n">
-        <v>22.19437034990764</v>
+        <v>21.95187866695868</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.8063179648229</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4357455417586</v>
+        <v>13.6279092420879</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11521196981113</v>
+        <v>73.75103825129919</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249630640370231</v>
+        <v>1.603283440245635</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.606360228326034</v>
+        <v>1.316523671394973</v>
       </c>
       <c r="C2" t="n">
-        <v>9.993209881528283</v>
+        <v>4.205807164993336</v>
       </c>
       <c r="D2" t="n">
-        <v>20.91711658668254</v>
+        <v>31.03991716517141</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.05371838629309</v>
+        <v>7.637997139040185</v>
       </c>
       <c r="C3" t="n">
-        <v>29.13827186204533</v>
+        <v>25.33890824661017</v>
       </c>
       <c r="D3" t="n">
-        <v>32.1031499288707</v>
+        <v>44.60570694245383</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.24542123052848</v>
+        <v>12.82653375598458</v>
       </c>
       <c r="C4" t="n">
-        <v>75.0703199529366</v>
+        <v>53.14396672628834</v>
       </c>
       <c r="D4" t="n">
-        <v>28.43534050580462</v>
+        <v>32.49388551516093</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.92194320974577</v>
+        <v>5.497787143782139</v>
       </c>
       <c r="C5" t="n">
-        <v>59.8375225738431</v>
+        <v>33.03581024790518</v>
       </c>
       <c r="D5" t="n">
-        <v>30.92505268377453</v>
+        <v>27.85709110800325</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.427682146153116</v>
       </c>
       <c r="C6" t="n">
-        <v>12.3572583533546</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72188819196585</v>
+        <v>14.83729340377435</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0035179709917</v>
+        <v>87.37517226667117</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180472047991462</v>
+        <v>2.472882233962391</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.772676500971245</v>
+        <v>0.9149888603580273</v>
       </c>
       <c r="C2" t="n">
-        <v>6.915430828714532</v>
+        <v>4.657411108946868</v>
       </c>
       <c r="D2" t="n">
-        <v>29.79211583307371</v>
+        <v>28.49424536805942</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.93729132011522</v>
+        <v>5.895394964002096</v>
       </c>
       <c r="C3" t="n">
-        <v>34.57224540505143</v>
+        <v>19.89511722656161</v>
       </c>
       <c r="D3" t="n">
-        <v>40.86033945075225</v>
+        <v>59.08648558009428</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.92559246312227</v>
+        <v>13.96241584979814</v>
       </c>
       <c r="C4" t="n">
-        <v>73.87062425834699</v>
+        <v>59.24454696047802</v>
       </c>
       <c r="D4" t="n">
-        <v>37.59897357724434</v>
+        <v>47.52836985799659</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.77025534167302</v>
+        <v>12.81180754042088</v>
       </c>
       <c r="C5" t="n">
-        <v>101.0218387669968</v>
+        <v>70.19496085364696</v>
       </c>
       <c r="D5" t="n">
-        <v>34.06664533736433</v>
+        <v>33.03581024790518</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.30442390377452</v>
+        <v>6.118251692866123</v>
       </c>
       <c r="C6" t="n">
-        <v>55.02401357992099</v>
+        <v>33.32837106377072</v>
       </c>
       <c r="D6" t="n">
-        <v>37.63529824230149</v>
+        <v>34.01264921363075</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.28809404570082</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.2097595180061</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.13486895504285</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03505418246903</v>
+        <v>16.0781548232218</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6572582380123</v>
+        <v>101.5462409887692</v>
       </c>
       <c r="D21" t="n">
-        <v>6.011684727489678</v>
+        <v>3.384874699625641</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.454590244795278</v>
+        <v>0.983711199655304</v>
       </c>
       <c r="C2" t="n">
-        <v>10.45757654563702</v>
+        <v>8.06113039957056</v>
       </c>
       <c r="D2" t="n">
-        <v>35.84066343893831</v>
+        <v>26.28040429498287</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.60487975900305</v>
+        <v>4.378594760940774</v>
       </c>
       <c r="C3" t="n">
-        <v>28.36759991421159</v>
+        <v>18.83482970597506</v>
       </c>
       <c r="D3" t="n">
-        <v>50.36856596638261</v>
+        <v>67.59823817591413</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.65458903902115</v>
+        <v>12.67338111412208</v>
       </c>
       <c r="C4" t="n">
-        <v>66.76178913189584</v>
+        <v>53.96078081622169</v>
       </c>
       <c r="D4" t="n">
-        <v>41.77238306799753</v>
+        <v>65.43446623575416</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.86780821729195</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="C5" t="n">
-        <v>88.82362354173019</v>
+        <v>90.7134878724053</v>
       </c>
       <c r="D5" t="n">
-        <v>32.10314992887071</v>
+        <v>41.79790850830796</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.6666888066416</v>
+        <v>11.79373517111693</v>
       </c>
       <c r="C6" t="n">
-        <v>72.73474216453346</v>
+        <v>74.54606667886881</v>
       </c>
       <c r="D6" t="n">
-        <v>30.5510068084565</v>
+        <v>36.99127174831558</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>32.09922293805371</v>
+        <v>33.59638818703009</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>36.89015173477814</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35868206941536</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.20104696185489</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.042226314307506</v>
+        <v>17.34554479008957</v>
       </c>
       <c r="C21" t="n">
-        <v>66.02087169663287</v>
+        <v>115.3478728540956</v>
       </c>
       <c r="D21" t="n">
-        <v>4.401391446442191</v>
+        <v>4.336386197522391</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.379576508645021</v>
+        <v>1.880046853632642</v>
       </c>
       <c r="C2" t="n">
-        <v>8.130834486572084</v>
+        <v>11.20763179168159</v>
       </c>
       <c r="D2" t="n">
-        <v>34.27870284148163</v>
+        <v>27.03045954102743</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.64200624531518</v>
+        <v>3.818998569520093</v>
       </c>
       <c r="C3" t="n">
-        <v>36.13322425480386</v>
+        <v>25.58434517267188</v>
       </c>
       <c r="D3" t="n">
-        <v>68.30509652297182</v>
+        <v>72.13391256953439</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.16357631817749</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="C4" t="n">
-        <v>69.46748580480005</v>
+        <v>50.29788013167683</v>
       </c>
       <c r="D4" t="n">
-        <v>58.47878375116551</v>
+        <v>82.49822308326797</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.3473430653209</v>
+        <v>18.13778883595982</v>
       </c>
       <c r="C5" t="n">
-        <v>108.5322087044849</v>
+        <v>94.34595437811849</v>
       </c>
       <c r="D5" t="n">
-        <v>40.37437433715008</v>
+        <v>53.82431788533139</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.31450342272425</v>
+        <v>17.02645043475243</v>
       </c>
       <c r="C6" t="n">
-        <v>112.4631265122891</v>
+        <v>109.3637490099819</v>
       </c>
       <c r="D6" t="n">
-        <v>33.85164259013428</v>
+        <v>41.62021217383928</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.402197763571703</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="C7" t="n">
-        <v>73.84019007951534</v>
+        <v>69.94756043217674</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>38.98618308334508</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>32.29459073119883</v>
+        <v>34.88149593188918</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>46.91183229972957</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.256144332522489</v>
+        <v>17.74648846576608</v>
       </c>
       <c r="C21" t="n">
-        <v>75.28249744992084</v>
+        <v>128.6620413768041</v>
       </c>
       <c r="D21" t="n">
-        <v>5.442108249391867</v>
+        <v>5.323946539729824</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.342270095883642</v>
+        <v>1.626755945936965</v>
       </c>
       <c r="C2" t="n">
-        <v>9.802750826904402</v>
+        <v>6.90364985626357</v>
       </c>
       <c r="D2" t="n">
-        <v>29.46421209985527</v>
+        <v>21.2518925538307</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.19883712007237</v>
+        <v>6.047565858160352</v>
       </c>
       <c r="C3" t="n">
-        <v>33.472687976295</v>
+        <v>41.37084825696059</v>
       </c>
       <c r="D3" t="n">
-        <v>79.16322613194156</v>
+        <v>79.93880681829654</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.61776565234527</v>
+        <v>8.70417514585222</v>
       </c>
       <c r="C4" t="n">
-        <v>80.50723873905544</v>
+        <v>78.47796623437728</v>
       </c>
       <c r="D4" t="n">
-        <v>77.86535566692727</v>
+        <v>74.7640146692116</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.88225669541517</v>
+        <v>9.572040116406402</v>
       </c>
       <c r="C5" t="n">
-        <v>119.503239299443</v>
+        <v>65.33530971762524</v>
       </c>
       <c r="D5" t="n">
-        <v>52.27806525114266</v>
+        <v>40.86524818927349</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.84156307118455</v>
+        <v>6.480516595733197</v>
       </c>
       <c r="C6" t="n">
-        <v>144.5436962439622</v>
+        <v>46.0478943199924</v>
       </c>
       <c r="D6" t="n">
-        <v>38.96360288614742</v>
+        <v>25.64030479181395</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.92983824910874</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>119.7732199181109</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>27.30829414132927</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>66.84229244364408</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>32.39374724932775</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.72718161587318</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.454964220698987</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>83.8683474828636</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.523093693111614</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
